--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,20 +41,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -143,19 +149,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,61 +158,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -834,23 +774,23 @@
       <c r="C4" s="3" t="n">
         <v>437.3</v>
       </c>
-      <c r="D4" s="10" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F4" s="10" t="n">
+      <c r="D4" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="3" t="n">
         <v>14</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>4.2</v>
@@ -862,32 +802,32 @@
       <c r="M4" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="N4" s="8" t="n">
+      <c r="N4" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>30</v>
+        <v>2.6</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>27</v>
+        <v>27.8</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>63.7</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
@@ -896,7 +836,7 @@
         <v>27.5</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>9.699999999999999</v>
@@ -915,19 +855,19 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E5" s="10" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E5" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="F5" s="10" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>5.7</v>
+      <c r="F5" s="12" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>57.2</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>16.3</v>
@@ -945,19 +885,19 @@
         <v>19.1</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>18</v>
+        <v>0.6</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>90</v>
+        <v>96.2</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>2.3</v>
+        <v>24.3</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>20.5</v>
+        <v>22.5</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>19.1</v>
@@ -966,13 +906,13 @@
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>87.8</v>
+        <v>82.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>60.6</v>
+        <v>61.6</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>18.9</v>
@@ -981,7 +921,7 @@
         <v>20.7</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>3.6</v>
@@ -1000,35 +940,37 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>438.6</v>
-      </c>
-      <c r="D6" s="10" t="n">
+        <v>431.6</v>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="12" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="12" t="n">
         <v>25.6</v>
       </c>
-      <c r="G6" s="10" t="n">
-        <v>11.6</v>
+      <c r="G6" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>17.8</v>
+        <v>12.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J6" s="3" t="n"/>
+      <c r="J6" s="3" t="n">
+        <v>3.6</v>
+      </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>60.6</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>19</v>
+      <c r="M6" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>21.1</v>
@@ -1037,7 +979,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>29.8</v>
@@ -1051,7 +993,7 @@
       <c r="T6" s="3" t="n">
         <v>61.9</v>
       </c>
-      <c r="U6" s="8" t="n">
+      <c r="U6" s="3" t="n">
         <v>16</v>
       </c>
       <c r="V6" s="3" t="n">
@@ -1064,10 +1006,10 @@
         <v>26.5</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>11.9</v>
+        <v>11.1</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1085,20 +1027,20 @@
       <c r="C7" s="3" t="n">
         <v>437.3</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="10" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F7" s="10" t="n">
+      <c r="E7" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="F7" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>14.8</v>
+      <c r="H7" s="3" t="n">
+        <v>4.2</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>3.4</v>
@@ -1107,25 +1049,25 @@
         <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L7" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="N7" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>17.3</v>
-      </c>
       <c r="O7" s="3" t="n">
-        <v>872.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="3" t="n">
-        <v>31.9</v>
+      <c r="Q7" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>23.9</v>
@@ -1134,25 +1076,25 @@
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>52.1</v>
+        <v>5.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>27.6</v>
+        <v>6.6</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>4.1</v>
+        <v>24.1</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>27.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>75.2</v>
+        <v>5.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1168,46 +1110,46 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>297.2</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="G8" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.1</v>
+        <v>4.4</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>18.5</v>
+        <v>24.5</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>18.6</v>
+      <c r="M8" s="8" t="n">
+        <v>865.6</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>87.2</v>
+        <v>82.7</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>21.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>26.6</v>
@@ -1222,22 +1164,22 @@
         <v>95.40000000000001</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>24</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>212.4</v>
+        <v>22.8</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>90.2</v>
+        <v>96.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>2.9</v>
+        <v>8.9</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1253,25 +1195,23 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6663.1</v>
+        <v>6.6</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>152.5</v>
+        <v>32.6</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>92.5</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>122.5</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>60.1</v>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="9" t="n">
+        <v>61.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>80.5</v>
+        <v>86.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>11.2</v>
+        <v>4.4</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
@@ -1283,7 +1223,7 @@
         <v>94.3</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>87.8</v>
+        <v>82.8</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>96.3</v>
@@ -1292,7 +1232,7 @@
         <v>440.9</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>4.4</v>
+        <v>12.9</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>138.8</v>
@@ -1301,7 +1241,7 @@
         <v>11.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>344.1</v>
+        <v>31.9</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>360.9</v>
@@ -1313,13 +1253,13 @@
         <v>126.1</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>29.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>2.8</v>
@@ -1338,7 +1278,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>333.3</v>
+        <v>333.2</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>30.5</v>
@@ -1346,30 +1286,32 @@
       <c r="E10" s="10" t="n">
         <v>18.5</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="12" t="n">
         <v>24.5</v>
       </c>
-      <c r="G10" s="10" t="n">
-        <v>12</v>
+      <c r="G10" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>16.1</v>
+        <v>1.6</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
+        <v>3.4</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>44.7</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="8" t="n">
-        <v>17.6</v>
+      <c r="M10" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>19.3</v>
+        <v>1.3</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>88.2</v>
@@ -1378,31 +1320,31 @@
         <v>2.6</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>27.8</v>
+        <v>82.2</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>26.4</v>
+        <v>2.6</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>11.7</v>
+        <v>2.2</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>25.2</v>
+        <v>25.8</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>80.5</v>
+        <v>806.5</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>6.6</v>
@@ -1421,19 +1363,19 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>445</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F11" s="10" t="n">
+        <v>445.6</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="G11" s="10" t="n">
-        <v>8.800000000000001</v>
+      <c r="G11" s="3" t="n">
+        <v>88.09999999999999</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
@@ -1442,7 +1384,7 @@
         <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>31.3</v>
+        <v>3.3</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1453,7 +1395,9 @@
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="N11" s="3" t="n"/>
+      <c r="N11" s="3" t="n">
+        <v>10.7</v>
+      </c>
       <c r="O11" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
@@ -1463,14 +1407,14 @@
       <c r="Q11" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="R11" s="8" t="n">
+      <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>5.7</v>
@@ -1481,11 +1425,11 @@
       <c r="W11" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="X11" s="8" t="n">
+      <c r="X11" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>97.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>0.8</v>
@@ -1506,17 +1450,17 @@
       <c r="C12" s="3" t="n">
         <v>383.6</v>
       </c>
-      <c r="D12" s="10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F12" s="10" t="n">
+      <c r="D12" s="12" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>23.9</v>
       </c>
-      <c r="G12" s="10" t="n">
-        <v>8.5</v>
+      <c r="G12" s="3" t="n">
+        <v>84.5</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>18</v>
@@ -1537,18 +1481,18 @@
         <v>19.3</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>61.1</v>
+        <v>21.5</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="R12" s="8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1558,13 +1502,13 @@
         <v>85.40000000000001</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>5.3</v>
+        <v>53.3</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>24.7</v>
+        <v>4.4</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>30.4</v>
@@ -1573,7 +1517,7 @@
         <v>97.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1589,22 +1533,22 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>256.7</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F13" s="10" t="n">
+        <v>356.1</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>25.5</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="12" t="n">
         <v>11.3</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.6</v>
+        <v>12.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.5</v>
@@ -1613,7 +1557,7 @@
         <v>2.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>20</v>
@@ -1622,22 +1566,22 @@
         <v>18.8</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>21.5</v>
+        <v>20.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>32.7</v>
+      <c r="S13" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>83.59999999999999</v>
@@ -1645,17 +1589,17 @@
       <c r="U13" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="V13" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>93.8</v>
+        <v>43.2</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>44.4</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.2</v>
@@ -1674,22 +1618,22 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="D14" s="10" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="10" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>12.9</v>
+      <c r="E14" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>22.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>2.8</v>
@@ -1698,16 +1642,16 @@
         <v>3.3</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>19.8</v>
+        <v>57.2</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>29.8</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.7</v>
+        <v>18.2</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>89.90000000000001</v>
@@ -1719,10 +1663,10 @@
         <v>30.6</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1740,7 +1684,7 @@
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>1.8</v>
@@ -1761,16 +1705,16 @@
       <c r="C15" s="3" t="n">
         <v>433.5</v>
       </c>
-      <c r="D15" s="10" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G15" s="10" t="n">
+      <c r="D15" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1783,16 +1727,16 @@
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N15" s="8" t="n">
-        <v>20.8</v>
+        <v>0.9</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>11.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>88.8</v>
@@ -1816,19 +1760,19 @@
         <v>14.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>24.5</v>
+        <v>4.5</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>74</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1844,18 +1788,18 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1992.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>149.9</v>
+        <v>7.8</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>99.09999999999999</v>
+        <v>929.1</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>124.7</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="G16" s="3" t="n">
         <v>50.8</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1871,47 +1815,49 @@
         <v>6</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>100.9</v>
+        <v>160.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>918.6</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>21122.2</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>0.4</v>
+        <v>11.1</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>12.9</v>
+        <v>8.9</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>83</v>
+        <v>23.7</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>445.1</v>
+        <v>42.5</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>368.7</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>53.1</v>
+        <v>533.4</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>120.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>451.1</v>
+        <v>46.4</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>315.1</v>
+        <v>7.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>455.1</v>
+        <v>45.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1926,8 +1872,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>399.2</v>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+3986
+</t>
+        </is>
       </c>
       <c r="D17" s="10" t="n">
         <v>30</v>
@@ -1936,19 +1886,19 @@
         <v>19.8</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G17" s="10" t="n">
-        <v>10.2</v>
+        <v>14.4</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>18.1</v>
+        <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n">
@@ -1958,7 +1908,7 @@
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>88.8</v>
@@ -1970,30 +1920,32 @@
         <v>28.6</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>24.6</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>28.5</v>
+        <v>22.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>73.7</v>
+        <v>3.7</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>42.8</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>43.2</v>
+        <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="Z17" s="3" t="n"/>
+        <v>1.9</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2008,58 +1960,58 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>137.3</v>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>24.9</v>
+        <v>43.2</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>64.40000000000001</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>81.8</v>
+        <v>11.2</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>17.7</v>
+        <v>12.7</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>21.9</v>
+        <v>82</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>42.9</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.2</v>
+        <v>23.1</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>6.1</v>
+        <v>63.1</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>4.4</v>
@@ -2074,10 +2026,14 @@
         <v>31</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>2.6</v>
+        <v>24.1</v>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+8 179
+</t>
+        </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2095,19 +2051,19 @@
       <c r="C19" s="3" t="n">
         <v>423.9</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="12" t="n">
         <v>32.6</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="12" t="n">
         <v>18.5</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="12" t="n">
         <v>25.4</v>
       </c>
-      <c r="G19" s="10" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H19" s="8" t="n">
+      <c r="G19" s="12" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="I19" s="3" t="n">
@@ -2117,16 +2073,16 @@
         <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>21.5</v>
+        <v>0.8</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>87.5</v>
@@ -2138,7 +2094,7 @@
         <v>31.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>94.2</v>
+        <v>24.2</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>25.3</v>
@@ -2150,19 +2106,27 @@
         <v>21.7</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>25.8</v>
+        <v>85.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y19" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z19" s="3" t="n">
-        <v>6.2</v>
+        <v>2</v>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+44
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+818
+</t>
+        </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2178,34 +2142,39 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>256.8</v>
-      </c>
-      <c r="D20" s="15" t="n">
-        <v>-93.8</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>-55.9</v>
-      </c>
-      <c r="F20" s="15" t="n">
-        <v>-74.90000000000001</v>
+        <v>3561.5</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+1 8 4
+7
+</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>18.8</v>
@@ -2214,13 +2183,13 @@
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>89</v>
+        <v>21.1</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>25.5</v>
+        <v>6.5</v>
+      </c>
+      <c r="Q20" s="8" t="n">
+        <v>535.2</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.5</v>
@@ -2229,7 +2198,7 @@
         <v>23.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>70.7</v>
+        <v>20.8</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>9.5</v>
@@ -2241,10 +2210,10 @@
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>67.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="Z20" s="3" t="n"/>
       <c r="AA20" s="3" t="inlineStr">
@@ -2263,20 +2232,18 @@
       <c r="C21" s="3" t="n">
         <v>433.5</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E21" s="10" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="E21" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="n">
-        <v>17.4</v>
+        <v>12.4</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.2</v>
@@ -2285,13 +2252,13 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>11.3</v>
+        <v>18.3</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>18.8</v>
@@ -2306,28 +2273,32 @@
         <v>30.1</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>21.7</v>
+        <v>41.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
+        <v>531</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>24.3</v>
+        <v>44.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>955.9</v>
+        <v>2.4</v>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+8111
+</t>
+        </is>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>250.4</v>
+        <v>850.1</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>4.5</v>
@@ -2346,22 +2317,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="G22" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>15.3</v>
+        <v>0.2</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.1</v>
@@ -2373,16 +2344,16 @@
         <v>3.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>17.6</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>87.5</v>
+        <v>1.5</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>87</v>
+        <v>872</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>2.6</v>
@@ -2397,22 +2368,22 @@
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>56.4</v>
+        <v>568.1</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>21.6</v>
+        <v>4.6</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>85.5</v>
+        <v>5.5</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>3.6</v>
@@ -2431,76 +2402,76 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>374</v>
+        <v>1985.5</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>31.8</v>
+        <v>653.4</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>17.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="G23" s="10" t="n">
-        <v>14.6</v>
+        <v>123</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>60.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>15.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.1</v>
+        <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3.5</v>
+        <v>15.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.7</v>
+        <v>49.2</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>17.6</v>
+        <v>95.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>16.2</v>
+        <v>882.6</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>96.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>87</v>
+        <v>438.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>146.9</v>
+        <v>146.2</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>215.4</v>
+        <v>2952.6</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>462.1</v>
+        <v>12.8</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>103.6</v>
+        <v>10.7</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>28.7</v>
+        <v>26.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>411</v>
+        <v>0.4</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2516,76 +2487,74 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1925.5</v>
+        <v>5851.1</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F24" s="28" t="n">
-        <v>23</v>
-      </c>
-      <c r="G24" s="10" t="n">
-        <v>60.3</v>
+        <v>30.6</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>3.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>85</v>
+        <v>12.6</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>11.6</v>
+        <v>2.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>49.2</v>
-      </c>
+        <v>3.1</v>
+      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n">
-        <v>95.2</v>
+        <v>19</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>88.2</v>
+        <v>12.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>96.5</v>
+        <v>1.3</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>437.2</v>
+        <v>872.4</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q24" s="8" t="n">
-        <v>46.9</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>29.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>14.3</v>
+        <v>22.9</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>19</v>
+        <v>23.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>215.4</v>
+        <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>462.1</v>
+        <v>4.4</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>103.6</v>
+        <v>22.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>28.7</v>
+        <v>0.9</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>411</v>
+        <v>0.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>7.1</v>
+        <v>0.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2601,76 +2570,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>385.1</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <v>12</v>
+        <v>34</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>87</v>
+        <v>18.8</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>19.3</v>
+        <v>0.1</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>60.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>21.7</v>
+        <v>0.5</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>29.2</v>
+        <v>324.3</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>22.9</v>
+        <v>24.3</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>23.8</v>
+        <v>1.8</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>59</v>
+        <v>56.9</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>17</v>
+        <v>19.7</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>24.4</v>
+        <v>7.1</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>22.1</v>
+        <v>20.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>85.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2686,49 +2655,49 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="D26" s="15" t="n">
-        <v>-89.90000000000001</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>-56.4</v>
-      </c>
-      <c r="F26" s="15" t="n">
-        <v>-73.2</v>
+        <v>34</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>45.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>12.8</v>
+        <v>0.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>31.6</v>
+        <v>36.3</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.4</v>
+        <v>7.5</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>20.4</v>
+        <v>18.1</v>
+      </c>
+      <c r="N26" s="8" t="n">
+        <v>60.4</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>31.3</v>
+        <v>324.3</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>24.3</v>
@@ -2743,19 +2712,19 @@
         <v>19.7</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>0.4</v>
+        <v>24.2</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>22.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>74.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2771,28 +2740,28 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>329.8</v>
-      </c>
-      <c r="D27" s="10" t="n">
+        <v>381.2</v>
+      </c>
+      <c r="D27" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="E27" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="12" t="n">
         <v>24.7</v>
       </c>
-      <c r="G27" s="10" t="n">
-        <v>12.2</v>
+      <c r="G27" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>31.6</v>
+        <v>2.6</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0.3</v>
@@ -2801,18 +2770,18 @@
         <v>19</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>18.4</v>
+        <v>12.6</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>87</v>
+        <v>87.2</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Q27" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2822,16 +2791,16 @@
         <v>24.5</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>24.2</v>
+        <v>6.1</v>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v>42.6</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>21.8</v>
+        <v>41.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>24.6</v>
@@ -2839,8 +2808,12 @@
       <c r="Y27" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="Z27" s="3" t="n">
-        <v>7.6</v>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+54
+</t>
+        </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2856,46 +2829,46 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>354.5</v>
-      </c>
-      <c r="D28" s="10" t="n">
+        <v>354.2</v>
+      </c>
+      <c r="D28" s="12" t="n">
         <v>28.2</v>
       </c>
-      <c r="E28" s="10" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F28" s="10" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G28" s="10" t="n">
-        <v>8.800000000000001</v>
+      <c r="E28" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>17.8</v>
+        <v>12.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>5.3</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>20.2</v>
+        <v>10.2</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>17.6</v>
+        <v>18.8</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>20.8</v>
+        <v>61.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>187.5</v>
+        <v>82.5</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>26</v>
@@ -2904,7 +2877,7 @@
         <v>21.6</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>68.40000000000001</v>
@@ -2913,19 +2886,19 @@
         <v>10.6</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>23.2</v>
+        <v>63.5</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>20.8</v>
+        <v>6.2</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>808.1</v>
+        <v>8.1</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2943,44 +2916,44 @@
       <c r="C29" s="3" t="n">
         <v>389.3</v>
       </c>
-      <c r="D29" s="10" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F29" s="10" t="n">
+      <c r="D29" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F29" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="G29" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>19.6</v>
+        <v>3.8</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>239.6</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>18.8</v>
+        <v>19.2</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>28.2</v>
@@ -2995,22 +2968,22 @@
         <v>64.90000000000001</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>13.4</v>
+        <v>1.4</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>26</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="X29" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="X29" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -3026,37 +2999,37 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>408.5</v>
+        <v>42.6</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>29.5</v>
+        <v>494.5</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>20.4</v>
+        <v>61.3</v>
       </c>
       <c r="F30" s="10" t="n">
         <v>24.9</v>
       </c>
-      <c r="G30" s="10" t="n">
+      <c r="G30" s="3" t="n">
         <v>9.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>20.1</v>
+        <v>4.1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.2</v>
+        <v>20.2</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>21.5</v>
@@ -3065,7 +3038,7 @@
         <v>90</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>12.9</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>28.6</v>
@@ -3080,10 +3053,10 @@
         <v>62.6</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>114.6</v>
+        <v>14.6</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>15.5</v>
+        <v>85.5</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>23</v>
@@ -3092,10 +3065,10 @@
         <v>26.5</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>6.1</v>
+        <v>2.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3111,61 +3084,61 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F31" s="28" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="F31" s="10" t="n">
         <v>24.1</v>
       </c>
-      <c r="G31" s="10" t="n">
-        <v>52.5</v>
+      <c r="G31" s="3" t="n">
+        <v>5.5</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>11.7</v>
+        <v>10</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.9</v>
+        <v>15.8</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>954.4</v>
+        <v>25.4</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N31" s="8" t="n">
-        <v>3.2</v>
+        <v>93.2</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>113.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>441.9</v>
+        <v>44.4</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2.3</v>
+        <v>13.1</v>
       </c>
       <c r="Q31" s="8" t="n">
-        <v>138.5</v>
+        <v>38.5</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>43.8</v>
+        <v>3.7</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>22.7</v>
+        <v>18.7</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>332.8</v>
+        <v>334.8</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>64.3</v>
+        <v>0.5</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>23.1</v>
@@ -3177,10 +3150,10 @@
         <v>24.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>399.8</v>
+        <v>322.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3196,46 +3169,48 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>371.3</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G32" s="10" t="n">
-        <v>10.5</v>
+        <v>437.3</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>10.1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
+        <v>3.2</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="L32" s="3" t="n">
-        <v>19.9</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>92.2</v>
+        <v>18.5</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>206.1</v>
+        <v>26.6</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Q32" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q32" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3245,25 +3220,29 @@
         <v>24.5</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>122.1</v>
+        <v>12.9</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>24.6</v>
+        <v>4.6</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>24.9</v>
+        <v>42.9</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>6.5</v>
+        <v>22.8</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+78
+</t>
+        </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3279,52 +3258,52 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="D33" s="10" t="n">
+        <v>3272</v>
+      </c>
+      <c r="D33" s="12" t="n">
         <v>32.8</v>
       </c>
-      <c r="E33" s="10" t="n">
+      <c r="E33" s="12" t="n">
         <v>20.2</v>
       </c>
-      <c r="F33" s="10" t="n">
+      <c r="F33" s="12" t="n">
         <v>26.5</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>6.6</v>
+      <c r="G33" s="12" t="n">
+        <v>12.6</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>20.6</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>18.6</v>
+        <v>19.3</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>21.5</v>
+        <v>61.5</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>28.4</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>31</v>
+        <v>0.1</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>25.4</v>
@@ -3336,19 +3315,19 @@
         <v>19.5</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>28.2</v>
+        <v>25.8</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>23.7</v>
+        <v>2.8</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>26.4</v>
+        <v>5.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3364,28 +3343,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>397</v>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E34" s="10" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E34" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F34" s="10" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G34" s="10" t="n">
+      <c r="F34" s="12" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>17.9</v>
+        <v>12.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
@@ -3394,46 +3373,50 @@
         <v>20.9</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>21.7</v>
+        <v>21.2</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>32.9</v>
+        <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>23.9</v>
+        <v>2.2</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>23.9</v>
+        <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>47.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>26.1</v>
+        <v>2.2</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>25.8</v>
+        <v>45.5</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>61.2</v>
+        <v>23.3</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>25.8</v>
+        <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>7.4</v>
+        <v>83.2</v>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+5
+</t>
+        </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3449,76 +3432,74 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>362.4</v>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F35" s="10" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="G35" s="10" t="n">
-        <v>10.2</v>
+        <v>884.5</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>3.4</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I35" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="J35" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>0</v>
+      <c r="K35" s="8" t="n">
+        <v>98</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>20.4</v>
+        <v>24.1</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>21</v>
+        <v>61.3</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>87.3</v>
+        <v>25.4</v>
       </c>
       <c r="P35" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="U35" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q35" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>25.5</v>
+      <c r="V35" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>23.3</v>
+        <v>20.3</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>27.2</v>
+        <v>2.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>83.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3534,76 +3515,74 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="D36" s="10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F36" s="10" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G36" s="10" t="n">
-        <v>3.9</v>
+        <v>398.9</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>8.6</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J36" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>289</v>
+      </c>
+      <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>2.9</v>
-      </c>
       <c r="Q36" s="3" t="n">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>21.2</v>
+        <v>23.1</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>24.3</v>
+        <v>25.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>88.5</v>
+        <v>72.3</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>3.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v>20.3</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="W36" s="3" t="n"/>
       <c r="X36" s="3" t="n">
-        <v>22.9</v>
+        <v>24.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>88.5</v>
+        <v>326.6</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3619,76 +3598,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>398.9</v>
-      </c>
-      <c r="D37" s="28" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E37" s="28" t="n">
-        <v>20</v>
-      </c>
-      <c r="F37" s="28" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="G37" s="10" t="n">
-        <v>8.6</v>
+        <v>1683.5</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>19</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.4</v>
+        <v>15.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>9</v>
+        <v>16.2</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>120.6</v>
+        <v>103.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>19.3</v>
+        <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>21.7</v>
+        <v>117.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>89</v>
+        <v>432.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>27</v>
+        <v>691.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>23.1</v>
+        <v>6.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>25.8</v>
+        <v>62.7</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>72.3</v>
+        <v>13.1</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>651.5</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>25</v>
+        <v>126.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>22.1</v>
+        <v>76.2</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>24.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>0.6</v>
+        <v>62.9</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3704,76 +3683,76 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1683.5</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F38" s="10" t="n">
+        <v>336.7</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="S38" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>163.5</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>437.5</v>
-      </c>
-      <c r="P38" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>399.6</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="S38" s="8" t="n">
-        <v>620.1</v>
-      </c>
       <c r="T38" s="3" t="n">
-        <v>343.7</v>
+        <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>65.7</v>
+        <v>13.1</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>26.1</v>
+        <v>52.6</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>44.4</v>
+        <v>0.1</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>4.4</v>
+        <v>35.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>396.6</v>
+        <v>0.1</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3789,76 +3768,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>336.7</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="G39" s="10" t="n">
-        <v>9.800000000000001</v>
+        <v>42.7</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>12.3</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>12.6</v>
+        <v>15.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>15.7</v>
+        <v>3.4</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>25.1</v>
+        <v>41.5</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>87.5</v>
+        <v>2.4</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>14.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>25.2</v>
+        <v>31.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>68.7</v>
+        <v>54.5</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.1</v>
+        <v>19.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>95.2</v>
+        <v>76.8</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>22.4</v>
+        <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>25.4</v>
+        <v>22.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>79.3</v>
+        <v>85.5</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3874,76 +3853,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="D40" s="15" t="n">
-        <v>-124.4</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>-76.3</v>
-      </c>
-      <c r="F40" s="15" t="n">
-        <v>-100.5</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>13.3</v>
+        <v>4.4</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>3.9</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>2.5</v>
+        <v>19</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>6.4</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.1</v>
+        <v>4.9</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>0.1</v>
+        <v>22.1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>88</v>
+        <v>88.8</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>23.1</v>
+        <v>19.8</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>23.6</v>
+        <v>22.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>54.5</v>
+        <v>89.7</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.2</v>
+        <v>2.6</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>26.8</v>
+        <v>21.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>77.8</v>
+        <v>1.6</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>25.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3959,76 +3938,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F41" s="10" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="G41" s="10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="N41" s="8" t="n">
+      <c r="Y41" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="O41" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="U41" s="3" t="n">
+      <c r="Z41" s="3" t="n">
         <v>2.6</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>3.6</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4043,77 +4022,81 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>448.8</v>
-      </c>
-      <c r="D42" s="10" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F42" s="10" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="G42" s="10" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>17.4</v>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">442
+2 6
+</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>25.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>10.4</v>
+        <v>4.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>19.9</v>
+        <v>12.2</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>19.1</v>
+        <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>20.8</v>
+        <v>12.6</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>12.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>28</v>
+        <v>24.7</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>21.6</v>
+        <v>22.3</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>21.7</v>
+        <v>25.4</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>58.4</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>16.1</v>
+        <v>5.2</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>24.6</v>
+        <v>63.2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>25.2</v>
+        <v>24.4</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>81.3</v>
+        <v>82</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>2.6</v>
+        <v>6.1</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4129,76 +4112,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="F43" s="10" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>25.8</v>
+        <v>341.3</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>13.4</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>15.6</v>
+        <v>16.9</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L43" s="8" t="n">
-        <v>78.09999999999999</v>
+        <v>15.2</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>16.1</v>
+        <v>17.7</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>17.6</v>
+        <v>19.4</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>89</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q43" s="8" t="n">
-        <v>30.8</v>
+        <v>2.4</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>22.6</v>
+        <v>66.3</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>22.2</v>
+        <v>12.3</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>50</v>
+        <v>21.1</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>23</v>
+        <v>6.3</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>21.4</v>
+        <v>61.1</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>87</v>
+        <v>0.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>0.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4214,76 +4197,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>341.3</v>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="E44" s="10" t="n">
+        <v>141.6</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F44" s="10" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="G44" s="10" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>16.9</v>
-      </c>
       <c r="I44" s="3" t="n">
-        <v>2.2</v>
+        <v>82.8</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>15.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>19</v>
+        <v>0.1</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>17.7</v>
+        <v>19.5</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>22.6</v>
+        <v>3.3</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="S44" s="8" t="n">
-        <v>22.3</v>
+        <v>2.2</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>92.3</v>
+        <v>3.2</v>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v>33.5</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>20.2</v>
+        <v>21.8</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>4.6</v>
+        <v>73.8</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4298,73 +4281,79 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>141.6</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="G45" s="10" t="n">
-        <v>4.9</v>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="12" t="n">
+        <v>173.4</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>143.4</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>18.6</v>
+        <v>12.6</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.8</v>
+        <v>13.3</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.6</v>
+        <v>165.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>30</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>41.4</v>
+        <v>26.4</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>19.8</v>
+        <v>1825.6</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>20.1</v>
+        <v>67.7</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P45" s="3" t="n"/>
-      <c r="Q45" s="3" t="n"/>
+        <v>37.2</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>26.2</v>
+      </c>
       <c r="R45" s="3" t="n">
-        <v>2.4</v>
+        <v>21.5</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>22</v>
+        <v>22.9</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>7.4</v>
+        <v>69</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>7.2</v>
+        <v>11.9</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>455.1</v>
+        <v>242.4</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>7.1</v>
+        <v>21.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y45" s="3" t="n">
-        <v>81.5</v>
+        <v>124.2</v>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 7
+57
+</t>
+        </is>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4380,43 +4369,46 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>311.7</v>
-      </c>
-      <c r="D46" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F46" s="15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G46" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G46" s="12" t="n">
         <v>10.1</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="I46" s="8" t="n">
-        <v>13.3</v>
+        <v>1.1</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>16.6</v>
+        <v>2.8</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>30</v>
+        <v>1.8</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>3.4</v>
+        <v>19.4</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>825.6</v>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20 8
+</t>
+        </is>
       </c>
       <c r="O46" s="3" t="n">
-        <v>324.1</v>
+        <v>89</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.4</v>
@@ -4425,29 +4417,31 @@
         <v>26.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>22.9</v>
-      </c>
+        <v>21.5</v>
+      </c>
+      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n">
         <v>69</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="8" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="W46" s="3" t="n"/>
+      <c r="X46" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="Y46" s="3" t="n"/>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 7
+57
+</t>
+        </is>
+      </c>
       <c r="Z46" s="3" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
@@ -41,12 +41,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -61,6 +55,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
   </fills>
@@ -772,75 +772,69 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>22.4</v>
+        <v>9437.5</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K4" s="3" t="n"/>
+        <v>14.2</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>17.5</v>
+      <c r="N4" s="8" t="n">
+        <v>82.5</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>87</v>
+        <v>187</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q4" s="8" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R4" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="R4" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="S4" s="3" t="n">
-        <v>27.8</v>
+      <c r="S4" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>63.7</v>
+        <v>631.1</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>22.2</v>
+        <v>18.1</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X4" s="3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -854,29 +848,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E5" s="12" t="n">
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E5" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="F5" s="12" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>57.2</v>
+      <c r="F5" s="11" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0.4</v>
+        <v>11.6</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="8" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>25.8</v>
@@ -885,46 +875,42 @@
         <v>19.1</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N5" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N5" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>24.3</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="3" t="n">
+      <c r="S5" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>82.8</v>
+        <v>187.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>4.2</v>
+        <v>12.9</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>18.9</v>
-      </c>
+        <v>20.6</v>
+      </c>
+      <c r="W5" s="3" t="inlineStr"/>
       <c r="X5" s="3" t="n">
-        <v>20.7</v>
+        <v>27.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>35</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>3.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -940,76 +926,74 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>431.6</v>
-      </c>
-      <c r="D6" s="12" t="n">
+        <v>432.4</v>
+      </c>
+      <c r="D6" s="11" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="11" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>3.6</v>
-      </c>
       <c r="K6" s="3" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>12</v>
+      <c r="M6" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>188.6</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="3" t="n">
-        <v>23.9</v>
+      <c r="R6" s="8" t="n">
+        <v>232.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>25.9</v>
+        <v>651.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>61.9</v>
+        <v>1608.9</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>26.5</v>
+        <v>20.7</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>11.1</v>
+        <v>185</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.5</v>
+        <v>13.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1025,76 +1009,74 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="D7" s="12" t="n">
+        <v>1437.3</v>
+      </c>
+      <c r="D7" s="8" t="n">
         <v>33</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>17</v>
+        <v>0.8</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="G7" s="12" t="n">
+        <v>251.1</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>17.3</v>
+      <c r="N7" s="8" t="n">
+        <v>67.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>187.6</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="8" t="n">
-        <v>18.9</v>
+      <c r="Q7" s="3" t="n">
+        <v>31.9</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="S7" s="3" t="n">
+      <c r="S7" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>5.1</v>
+        <v>2022.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W7" s="3" t="n">
+      <c r="V7" s="8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="W7" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>2.8</v>
+      <c r="X7" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>5.2</v>
+        <v>177.9</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1110,61 +1092,61 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="G8" s="3" t="n">
+        <v>1297.2</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G8" s="11" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.2</v>
+        <v>17.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>4.4</v>
+        <v>16.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K8" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="L8" s="3" t="n">
+      <c r="K8" s="8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="L8" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>865.6</v>
-      </c>
-      <c r="N8" s="3" t="n">
+      <c r="M8" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="N8" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>82.7</v>
+        <v>187.7</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q8" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="Q8" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S8" s="8" t="n">
         <v>33.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>2524.1</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>24</v>
@@ -1172,14 +1154,14 @@
       <c r="W8" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X8" s="3" t="n">
-        <v>22</v>
+      <c r="X8" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>96.2</v>
+        <v>90.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1195,24 +1177,20 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="9" t="n">
-        <v>61.1</v>
+        <v>1666.5</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>852.6</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr"/>
+      <c r="G9" s="12" t="n">
+        <v>68.09999999999999</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>80.5</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
@@ -1220,49 +1198,43 @@
         <v>44.3</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>94.3</v>
+        <v>194.3</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>82.8</v>
+        <v>187.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>96.3</v>
+        <v>196.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>440.9</v>
+        <v>1440.9</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>12.9</v>
+        <v>162.9</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>138.8</v>
+        <v>1138.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>11.3</v>
+        <v>1617.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>31.9</v>
+        <v>132.9</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>360.9</v>
+        <v>1360.9</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>126.1</v>
-      </c>
-      <c r="W9" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>1126.1</v>
+      </c>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="inlineStr"/>
       <c r="Z9" s="3" t="n">
-        <v>2.8</v>
+        <v>32.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1278,76 +1250,72 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>333.2</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F10" s="12" t="n">
+        <v>333.3</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>1.6</v>
+        <v>12</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>16.1</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="L10" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="M10" s="8" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="n">
-        <v>88.2</v>
+        <v>188.2</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="R10" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="R10" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="S10" s="3" t="n">
-        <v>2.6</v>
+      <c r="S10" s="8" t="n">
+        <v>26.4</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>2.2</v>
+        <v>272.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>0.4</v>
+        <v>11.7</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>25.8</v>
+        <v>0.5</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>2.6</v>
+        <v>22.6</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>806.5</v>
+        <v>180.5</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>6.6</v>
+        <v>16.6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1363,77 +1331,73 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>445.6</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="F11" s="3" t="n">
+        <v>1445</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F11" s="11" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3.3</v>
+        <v>13.3</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="3" t="n">
-        <v>20.1</v>
-      </c>
+      <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="N11" s="3" t="n">
-        <v>10.7</v>
+      <c r="N11" s="8" t="n">
+        <v>20.7</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>187.9</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>27.9</v>
+        <v>41.9</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="S11" s="3" t="n">
-        <v>31.9</v>
+      <c r="S11" s="8" t="n">
+        <v>981.9</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="U11" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="V11" s="3" t="n">
+      <c r="U11" s="8" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="V11" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>197.5</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1450,32 +1414,32 @@
       <c r="C12" s="3" t="n">
         <v>383.6</v>
       </c>
-      <c r="D12" s="12" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F12" s="12" t="n">
+      <c r="D12" s="11" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>23.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>84.5</v>
+        <v>18.5</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.9</v>
+        <v>12.9</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>20.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>19.3</v>
@@ -1487,10 +1451,10 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>22.7</v>
+        <v>20.7</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>72.2</v>
+        <v>27.8</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>25.2</v>
@@ -1499,25 +1463,25 @@
         <v>30.8</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>8544.1</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="V12" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X12" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="X12" s="8" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>97.7</v>
+        <v>197.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1533,33 +1497,33 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>356.1</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F13" s="12" t="n">
+        <v>39356.7</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F13" s="11" t="n">
         <v>25.5</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="11" t="n">
         <v>11.3</v>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>12.6</v>
+      <c r="H13" s="8" t="n">
+        <v>17.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L13" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="L13" s="8" t="n">
         <v>20</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1569,40 +1533,38 @@
         <v>20.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>2.5</v>
-      </c>
+        <v>189.1</v>
+      </c>
+      <c r="P13" s="3" t="inlineStr"/>
       <c r="Q13" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="S13" s="8" t="n">
-        <v>24.7</v>
+      <c r="S13" s="3" t="n">
+        <v>32.7</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="U13" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="V13" s="3" t="n">
+      <c r="U13" s="8" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="V13" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="3" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="X13" s="3" t="n">
+      <c r="W13" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X13" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>44.4</v>
+        <v>197.7</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.2</v>
+        <v>10.7</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1618,43 +1580,41 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>340.8</v>
-      </c>
-      <c r="D14" s="12" t="n">
+        <v>13974</v>
+      </c>
+      <c r="D14" s="11" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="12" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>22.9</v>
+      <c r="E14" s="11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>12.2</v>
+        <v>17.2</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>3.3</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>57.2</v>
+        <v>5.7</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>189.9</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>2.3</v>
@@ -1663,10 +1623,10 @@
         <v>30.6</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>2.6</v>
+        <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>2.3</v>
+        <v>22.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1680,11 +1640,11 @@
       <c r="W14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="3" t="n">
+      <c r="X14" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>1.8</v>
@@ -1705,41 +1665,39 @@
       <c r="C15" s="3" t="n">
         <v>433.5</v>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>44.1</v>
+      <c r="D15" s="11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>24.9</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H15" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H15" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>26.4</v>
+        <v>20.4</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="N15" s="3" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>88.8</v>
+        <v>188.8</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>2.6</v>
@@ -1750,29 +1708,29 @@
       <c r="R15" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S15" s="3" t="n">
+      <c r="S15" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>63.8</v>
+        <v>163.8</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="V15" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>21.1</v>
+      <c r="V15" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>241.1</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>2.8</v>
+        <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>11.5</v>
+        <v>174</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>7.2</v>
+        <v>17.9</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1788,76 +1746,70 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>929.1</v>
-      </c>
-      <c r="F16" s="10" t="n">
+        <v>11992.8</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F16" s="11" t="n">
         <v>124.7</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>50.8</v>
+      <c r="G16" s="12" t="n">
+        <v>15.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>11.1</v>
-      </c>
+        <v>190.3</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>160.9</v>
+        <v>1100.9</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>21122.2</v>
+        <v>105.2</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>11.1</v>
+        <v>444.1</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>8.9</v>
+        <v>12.9</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>142.8</v>
+        <v>1142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>23.7</v>
+        <v>123</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>42.5</v>
+        <v>142.5</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>368.7</v>
+        <v>1368.7</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>533.4</v>
+        <v>533441.5</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="3" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>7.3</v>
-      </c>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>45.1</v>
+        <v>1455.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>3.4</v>
+        <v>13.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1872,79 +1824,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-3986
-</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="n">
+      <c r="C17" s="3" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="D17" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>14.4</v>
+      <c r="F17" s="11" t="n">
+        <v>24.9</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>2.2</v>
+        <v>18.1</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>1</v>
+      <c r="N17" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>88.8</v>
+        <v>188.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="3" t="n">
-        <v>28.6</v>
+      <c r="Q17" s="8" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>22.5</v>
+        <v>946.4</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>6.6</v>
+        <v>173.7</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>10.6</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>42.8</v>
+        <v>24.2</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>2.5</v>
+        <v>27.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>1.9</v>
+        <v>191</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>2.7</v>
+        <v>12.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1960,31 +1908,29 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="D18" s="3" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="D18" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>3.5</v>
+      <c r="E18" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="8" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>39.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.6</v>
+        <v>18</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>19.2</v>
@@ -1996,44 +1942,40 @@
         <v>19.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="P18" s="8" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="Q18" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Q18" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S18" s="3" t="n">
+      <c r="S18" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>63.1</v>
+        <v>163.1</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V18" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V18" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>31</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-8 179
-</t>
-        </is>
+        <v>92.09999999999999</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2049,46 +1991,46 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>423.9</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E19" s="12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>25.4</v>
+        <v>1423.9</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>25.5</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>14.2</v>
+        <v>12.5</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.9</v>
+        <v>16.1</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.3</v>
+        <v>13.5</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.8</v>
+        <v>28.5</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>18.2</v>
+      <c r="M19" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>87.5</v>
+        <v>2.3</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>31.8</v>
@@ -2100,33 +2042,25 @@
         <v>25.3</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>54</v>
+        <v>62.1</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="3" t="n">
-        <v>85.8</v>
+      <c r="V19" s="8" t="n">
+        <v>25.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-44
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-818
-</t>
-        </is>
+      <c r="X19" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y19" s="3" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2142,80 +2076,77 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3561.5</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E20" s="3" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E20" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="11" t="n">
         <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-1 8 4
-7
-</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>82.8</v>
+        <v>17.4</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="M20" s="3" t="n">
+      <c r="K20" s="8" t="n">
+        <v>2408</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="M20" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>21.1</v>
+        <v>189</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q20" s="8" t="n">
-        <v>535.2</v>
-      </c>
-      <c r="R20" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R20" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>20.8</v>
+        <v>70.7</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>9.5</v>
+        <v>19.5</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="3" t="n">
+      <c r="W20" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>2.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+        <v>167.2</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2230,78 +2161,72 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>433.5</v>
-      </c>
-      <c r="D21" s="12" t="n">
+        <v>1433.5</v>
+      </c>
+      <c r="D21" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="E21" s="12" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="G21" s="3" t="n"/>
+      <c r="E21" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>12.4</v>
+      </c>
       <c r="H21" s="3" t="n">
-        <v>12.4</v>
+        <v>17.7</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>18.3</v>
+        <v>1.4</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q21" s="3" t="n">
+        <v>186.7</v>
+      </c>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="8" t="n">
         <v>30.1</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>41.7</v>
+        <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>531</v>
+        <v>151</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="V21" s="3" t="n">
-        <v>44.3</v>
+      <c r="V21" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-8111
-</t>
-        </is>
+        <v>2.2</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>25.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>850.1</v>
+        <v>185</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2317,46 +2242,46 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="G22" s="3" t="n">
+        <v>374</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G22" s="11" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.2</v>
+        <v>15.5</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.1</v>
+        <v>21.1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>12.5</v>
+        <v>17.6</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.5</v>
+        <v>17.5</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>872</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>2.6</v>
+        <v>187</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>30.2</v>
@@ -2364,26 +2289,26 @@
       <c r="R22" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="S22" s="3" t="n">
+      <c r="S22" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>568.1</v>
+        <v>156.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="3" t="n">
-        <v>21.8</v>
+      <c r="V22" s="8" t="n">
+        <v>21.2</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>4.6</v>
+      <c r="X22" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>5.5</v>
+        <v>185.5</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>3.6</v>
@@ -2402,19 +2327,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1985.5</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>653.4</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>123</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>60.3</v>
+        <v>1925.5</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>122.9</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>16</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2423,55 +2348,47 @@
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>15.5</v>
+        <v>135.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>95.2</v>
+        <v>195.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>882.6</v>
+        <v>1882.8</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>96.5</v>
+        <v>196.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>438.2</v>
+        <v>1437.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>4.3</v>
-      </c>
+        <v>13.7</v>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2952.6</v>
+        <v>1295.2</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="V23" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>10.7</v>
-      </c>
+        <v>85.2</v>
+      </c>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr"/>
       <c r="X23" s="3" t="n">
-        <v>26.7</v>
+        <v>1126.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>0.4</v>
+        <v>1411</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>2.1</v>
+        <v>27.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2487,22 +2404,22 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5851.1</v>
-      </c>
-      <c r="D24" s="10" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="D24" s="11" t="n">
         <v>30.6</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="11" t="n">
         <v>24.6</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>12.6</v>
+      <c r="G24" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2510,23 +2427,21 @@
       <c r="J24" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K24" s="3" t="n"/>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>1.3</v>
+      <c r="M24" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="N24" s="8" t="n">
+        <v>19.5</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>872.4</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q24" s="3" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="8" t="n">
         <v>29.2</v>
       </c>
       <c r="R24" s="3" t="n">
@@ -2536,25 +2451,25 @@
         <v>23.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>59</v>
+        <v>159</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>4.4</v>
+        <v>17.6</v>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="X24" s="3" t="n">
-        <v>0.9</v>
+      <c r="X24" s="8" t="n">
+        <v>25.3</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>0.8</v>
+        <v>182.2</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2570,19 +2485,19 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>45.1</v>
+        <v>1374</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.1</v>
+        <v>9.1</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>18.8</v>
@@ -2591,55 +2506,53 @@
         <v>2.4</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>13.6</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr"/>
       <c r="L25" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>0.1</v>
+        <v>18.4</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>60.4</v>
+        <v>20.4</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>324.3</v>
+        <v>2.2</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>31.3</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>1.8</v>
+        <v>243.1</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>56.9</v>
+        <v>956.9</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W25" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="W25" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="3" t="n">
-        <v>66.09999999999999</v>
+      <c r="X25" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>74.8</v>
+        <v>1747.6</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2655,76 +2568,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>2.4</v>
+        <v>329.8</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>36.3</v>
+        <v>12.6</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>7.5</v>
+        <v>10.3</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>18.1</v>
+        <v>1.6</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>60.4</v>
+        <v>949.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>90</v>
+        <v>187</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>2.2</v>
+        <v>12.8</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>324.3</v>
+        <v>24.4</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>24.3</v>
+        <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>25.9</v>
+        <v>24.5</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>56.9</v>
+        <v>180</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V26" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V26" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>6.8</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>74.8</v>
+        <v>181.1</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.5</v>
+        <v>17.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2740,80 +2653,74 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>381.2</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>24.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.8</v>
+        <v>18.8</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>2.6</v>
+        <v>17.8</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="8" t="n">
+        <v>21.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>19</v>
+        <v>5.3</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>19.2</v>
+        <v>18.8</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>87.2</v>
+        <v>187.5</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>24.4</v>
+        <v>21.9</v>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>24.5</v>
+        <v>23</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>86</v>
+        <v>168.4</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>6.1</v>
+        <v>10.6</v>
       </c>
       <c r="V27" s="8" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>24.6</v>
+        <v>23.2</v>
+      </c>
+      <c r="W27" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>23</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-54
-</t>
-        </is>
+        <v>180.8</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>5.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2829,76 +2736,76 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>354.2</v>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E28" s="12" t="n">
+        <v>9389.299999999999</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="M28" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>61.2</v>
+      <c r="N28" s="8" t="n">
+        <v>21.3</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>82.5</v>
+        <v>187.4</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="Q28" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R28" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V28" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="R28" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>63.5</v>
-      </c>
       <c r="W28" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>23</v>
+        <v>23.6</v>
+      </c>
+      <c r="X28" s="8" t="n">
+        <v>27.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>8.1</v>
+        <v>82</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2914,76 +2821,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>389.3</v>
-      </c>
-      <c r="D29" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E29" s="9" t="n">
+        <v>408.5</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K29" s="8" t="n">
-        <v>239.6</v>
-      </c>
       <c r="L29" s="3" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>28.2</v>
+        <v>21.3</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="3" t="n">
-        <v>24.8</v>
+      <c r="S29" s="8" t="n">
+        <v>226.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>162.6</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>26</v>
+        <v>14.6</v>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v>25.5</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>27.6</v>
+        <v>23</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>26.5</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>82</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>6.1</v>
+        <v>16.1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2999,76 +2906,76 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>494.5</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>9.1</v>
+        <v>1856.4</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>150.3</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>15.2</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>4.1</v>
+        <v>191.9</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1</v>
+        <v>180</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2.9</v>
+        <v>15.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>20.2</v>
+        <v>125.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>20.3</v>
+        <v>199.6</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>19.5</v>
+        <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>21.5</v>
+        <v>1103.2</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>90</v>
+        <v>1441.9</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2.3</v>
+        <v>13.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>28.6</v>
+        <v>1138.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>23</v>
+        <v>1113.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>24.5</v>
+        <v>122.8</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>62.6</v>
+        <v>1332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>14.6</v>
+        <v>164.5</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>85.5</v>
+        <v>1823.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>23</v>
+        <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>26.5</v>
+        <v>1124.3</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>1399.8</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>2.6</v>
+        <v>32.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3084,76 +2991,74 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>24.1</v>
+        <v>383.1</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>2.9</v>
+        <v>184.5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>25.4</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>19.9</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>93.2</v>
+        <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>113.6</v>
+        <v>6.4</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>44.4</v>
+        <v>188.4</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
       <c r="Q31" s="8" t="n">
-        <v>38.5</v>
+        <v>27.7</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>3.7</v>
+        <v>22.7</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>18.7</v>
+        <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>334.8</v>
+        <v>166.6</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>0.5</v>
+        <v>12.9</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>23.1</v>
+        <v>24.6</v>
       </c>
       <c r="W31" s="8" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>24.3</v>
+        <v>22</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>94.90000000000001</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>322.8</v>
+        <v>80</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.2</v>
+        <v>6.5</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3171,78 +3076,70 @@
       <c r="C32" s="3" t="n">
         <v>437.3</v>
       </c>
-      <c r="D32" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F32" s="12" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="D32" s="11" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2</v>
+        <v>13.5</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.2</v>
+        <v>14.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>20.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>18.5</v>
+        <v>12.3</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>26.6</v>
+        <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>2.6</v>
-      </c>
+        <v>188.4</v>
+      </c>
+      <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="3" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>22.7</v>
+        <v>31</v>
+      </c>
+      <c r="R32" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>24.5</v>
+        <v>25.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>66.5</v>
+        <v>156.6</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>12.9</v>
+        <v>19.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>42.9</v>
+        <v>23.7</v>
+      </c>
+      <c r="X32" s="8" t="n">
+        <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-78
-</t>
-        </is>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>1118.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3258,76 +3155,74 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>3272</v>
-      </c>
-      <c r="D33" s="12" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G33" s="12" t="n">
-        <v>12.6</v>
+        <v>1397</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>34.1</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>18.2</v>
+        <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>4.3</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="3" t="n">
-        <v>0.8</v>
+        <v>10</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>20.9</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>19.3</v>
+        <v>49.5</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>61.5</v>
+        <v>26.7</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>28.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>0.1</v>
+        <v>3.1</v>
+      </c>
+      <c r="Q33" s="8" t="n">
+        <v>32.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>44</v>
+        <v>23.9</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>25.4</v>
+        <v>63.4</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="V33" s="3" t="n">
+        <v>1947.7</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="W33" s="3" t="n">
-        <v>2.8</v>
+      <c r="W33" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>5.8</v>
+        <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>2.6</v>
+        <v>127.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0.3</v>
+        <v>17.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3343,80 +3238,74 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F34" s="12" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>13.9</v>
+        <v>362.4</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="G34" s="11" t="n">
+        <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I34" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="I34" s="3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="J34" s="3" t="n">
-        <v>5.5</v>
+        <v>12.6</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>2.9</v>
-      </c>
+        <v>187.3</v>
+      </c>
+      <c r="P34" s="3" t="inlineStr"/>
       <c r="Q34" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S34" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="S34" s="8" t="n">
         <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>2.2</v>
+        <v>17.2</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>45.5</v>
+        <v>55.4</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X34" s="3" t="n">
+      <c r="X34" s="8" t="n">
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-5
-</t>
-        </is>
+        <v>183.2</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3432,52 +3321,54 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>884.5</v>
-      </c>
-      <c r="D35" s="12" t="n">
+        <v>187.9</v>
+      </c>
+      <c r="D35" s="11" t="n">
         <v>24.7</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="11" t="n">
         <v>20.8</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="11" t="n">
         <v>22.6</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3.4</v>
+        <v>23.9</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="I35" s="3" t="n"/>
+      <c r="I35" s="3" t="n">
+        <v>10.3</v>
+      </c>
       <c r="J35" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K35" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>24.1</v>
+        <v>10.4</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N35" s="3" t="n">
-        <v>61.3</v>
+      <c r="N35" s="8" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>25.4</v>
+        <v>854.1</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q35" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Q35" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S35" s="3" t="n">
+      <c r="S35" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="T35" s="3" t="n">
@@ -3492,14 +3383,14 @@
       <c r="W35" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="X35" s="3" t="n">
+      <c r="X35" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="Z35" s="3" t="n">
         <v>2.9</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>0.6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3517,17 +3408,17 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="12" t="n">
+      <c r="D36" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>24.8</v>
+      <c r="E36" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>24.3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>19</v>
@@ -3539,7 +3430,7 @@
         <v>2.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>20.6</v>
@@ -3547,23 +3438,23 @@
       <c r="M36" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>21.2</v>
+      <c r="N36" s="8" t="n">
+        <v>21.7</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>289</v>
+        <v>189</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="R36" s="3" t="n">
+      <c r="Q36" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="R36" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>25.8</v>
+      <c r="S36" s="8" t="n">
+        <v>593.8</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>72.3</v>
@@ -3571,18 +3462,20 @@
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="W36" s="3" t="n"/>
-      <c r="X36" s="3" t="n">
+      <c r="V36" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W36" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X36" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>326.6</v>
+        <v>178.2</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.4</v>
+        <v>16.9</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3598,22 +3491,22 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1683.5</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>124.9</v>
+        <v>11683.5</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>150.1</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>125.5</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>192.4</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
@@ -3622,52 +3515,44 @@
         <v>15.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>16.2</v>
+        <v>160.8</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="3" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>117.2</v>
-      </c>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>432.5</v>
+        <v>1432.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.9</v>
+        <v>14.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>691.6</v>
+        <v>139.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>6.4</v>
+        <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>62.7</v>
+        <v>126.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>13.1</v>
+        <v>3431.1</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>651.5</v>
+        <v>165.7</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>72.09999999999999</v>
-      </c>
+      <c r="W37" s="3" t="inlineStr"/>
+      <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>79.3</v>
+        <v>396.6</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>62.9</v>
+        <v>342.4</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3685,74 +3570,72 @@
       <c r="C38" s="3" t="n">
         <v>336.7</v>
       </c>
-      <c r="D38" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="G38" s="3" t="n">
+      <c r="D38" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="G38" s="11" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="H38" s="8" t="n">
-        <v>82.5</v>
+      <c r="H38" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>7.4</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>211.1</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>44.4</v>
+        <v>21.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>87.5</v>
+        <v>187.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>17.9</v>
+        <v>27.9</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S38" s="3" t="n">
+      <c r="S38" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>68.7</v>
+        <v>168.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>52.6</v>
+        <v>18.1</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>0.1</v>
+        <v>22.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>35.4</v>
+        <v>25.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>0.1</v>
+        <v>79.3</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>0.6</v>
+        <v>18.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3768,76 +3651,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="D39" s="12" t="n">
+        <v>1400.8</v>
+      </c>
+      <c r="D39" s="11" t="n">
         <v>31.9</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="F39" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="G39" s="11" t="n">
         <v>12.3</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>15.5</v>
+        <v>52.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>41.5</v>
+        <v>10</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>20.5</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="3" t="n">
+      <c r="N39" s="8" t="n">
         <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>31.4</v>
+        <v>91</v>
+      </c>
+      <c r="P39" s="8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>30.4</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>31.6</v>
+        <v>23.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>54.5</v>
+        <v>345.1</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="3" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="W39" s="3" t="n">
+      <c r="V39" s="8" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="W39" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="X39" s="3" t="n">
-        <v>22.6</v>
+      <c r="X39" s="8" t="n">
+        <v>27.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>85.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.6</v>
+        <v>17.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3853,31 +3736,31 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F40" s="12" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F40" s="11" t="n">
         <v>22.1</v>
       </c>
-      <c r="G40" s="12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H40" s="3" t="n">
+      <c r="G40" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H40" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="I40" s="8" t="n">
-        <v>6.4</v>
+      <c r="I40" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>4.9</v>
+        <v>14.9</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>20.4</v>
@@ -3886,16 +3769,16 @@
         <v>19.1</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>22.1</v>
+        <v>10.1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>88.8</v>
+        <v>88</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.7</v>
+        <v>18.7</v>
       </c>
       <c r="Q40" s="8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>19.8</v>
@@ -3904,7 +3787,7 @@
         <v>22.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>89.7</v>
+        <v>189.7</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>2.6</v>
@@ -3913,16 +3796,16 @@
         <v>21.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>21.2</v>
+        <v>19.6</v>
+      </c>
+      <c r="X40" s="8" t="n">
+        <v>21.7</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>81.3</v>
+        <v>85.5</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3938,40 +3821,40 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="D41" s="12" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E41" s="12" t="n">
+        <v>1448.8</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E41" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="F41" s="12" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="G41" s="12" t="n">
-        <v>9.9</v>
+      <c r="F41" s="11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>12.4</v>
+        <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.1</v>
+        <v>13</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="L41" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L41" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>10.8</v>
+        <v>20.8</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>89.09999999999999</v>
@@ -3982,32 +3865,32 @@
       <c r="Q41" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>58.4</v>
+        <v>584.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>28.5</v>
+        <v>4.6</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>0.1</v>
+        <v>174</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2.6</v>
+        <v>19.6</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4022,81 +3905,77 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">442
-2 6
-</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="F42" s="12" t="n">
+      <c r="C42" s="3" t="n">
+        <v>464.3</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="F42" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="G42" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>5.8</v>
+        <v>20.1</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>12.2</v>
+        <v>2.8</v>
+      </c>
+      <c r="L42" s="8" t="n">
+        <v>72.8</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>16.1</v>
+        <v>16.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>12.6</v>
+        <v>17.6</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>89</v>
+        <v>289</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>2.1</v>
+        <v>12.1</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>24.7</v>
+        <v>30.8</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>25.4</v>
+        <v>22.6</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>5.2</v>
+        <v>130</v>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v>22.2</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>63.2</v>
+        <v>27.5</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>21.4</v>
+        <v>23.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>24.4</v>
+        <v>0.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>6.1</v>
+        <v>3.7</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4112,25 +3991,25 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>341.3</v>
-      </c>
-      <c r="D43" s="12" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E43" s="12" t="n">
+        <v>2341.3</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E43" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G43" s="12" t="n">
+      <c r="F43" s="11" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="G43" s="11" t="n">
         <v>13.4</v>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>2.2</v>
+        <v>24.9</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>2.8</v>
@@ -4151,37 +4030,37 @@
         <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>66.3</v>
+        <v>12.5</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="R43" s="8" t="n">
+        <v>22.3</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>12.3</v>
+        <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>21.1</v>
+        <v>181.4</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>61.1</v>
+        <v>15.7</v>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>791.4</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>0.8</v>
+        <v>182.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>4.6</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4199,75 +4078,69 @@
       <c r="C44" s="3" t="n">
         <v>141.6</v>
       </c>
-      <c r="D44" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="E44" s="12" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G44" s="3" t="n">
+      <c r="D44" s="11" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G44" s="11" t="n">
         <v>4.9</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>82.8</v>
+        <v>10.8</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1</v>
+        <v>19.4</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>19.5</v>
+        <v>1.4</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>20.1</v>
+        <v>6.5</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>89</v>
+        <v>390.1</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>3.3</v>
+        <v>12.4</v>
+      </c>
+      <c r="Q44" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>2.2</v>
+        <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>22.9</v>
+        <v>22.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>7</v>
+        <v>181</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v>33.5</v>
+        <v>15.1</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>73.8</v>
-      </c>
+        <v>20.2</v>
+      </c>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4281,79 +4154,65 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="12" t="n">
-        <v>173.4</v>
-      </c>
-      <c r="E45" s="12" t="n">
-        <v>113.4</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>143.4</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="C45" s="3" t="n">
+        <v>16871.1</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>174</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>114</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>143.7</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
       <c r="I45" s="3" t="n">
-        <v>13.3</v>
+        <v>123.3</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>165.6</v>
+        <v>116.6</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>30</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>1825.6</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>67.7</v>
-      </c>
+        <v>110.4</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>37.2</v>
+        <v>10234.2</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.4</v>
+        <v>1167.4</v>
       </c>
       <c r="Q45" s="3" t="n">
+        <v>1691.2</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="S45" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R45" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>22.9</v>
-      </c>
       <c r="T45" s="3" t="n">
-        <v>69</v>
+        <v>4084.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V45" s="3" t="n">
-        <v>242.4</v>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v>21.8</v>
-      </c>
+        <v>112.2</v>
+      </c>
+      <c r="V45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="inlineStr"/>
       <c r="X45" s="3" t="n">
-        <v>124.2</v>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 7
-57
-</t>
-        </is>
+        <v>184832438.2</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>81.5</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>5.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4369,43 +4228,38 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D46" s="12" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E46" s="12" t="n">
+        <v>311.7</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E46" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="F46" s="12" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G46" s="12" t="n">
+      <c r="F46" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="G46" s="11" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="3" t="n">
-        <v>1.1</v>
+      <c r="H46" s="8" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>825.6</v>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20 8
-</t>
-        </is>
+      <c r="M46" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>89</v>
@@ -4413,36 +4267,34 @@
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
+      <c r="Q46" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>22.9</v>
+      </c>
       <c r="T46" s="3" t="n">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 7
-57
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="W46" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
@@ -47,8 +47,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -59,8 +59,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,10 +146,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,7 +173,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -772,62 +796,64 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>9437.5</v>
-      </c>
-      <c r="D4" s="8" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="D4" s="11" t="n">
         <v>31.2</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="F4" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>14.4</v>
+      <c r="E4" s="11" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>91241.10000000001</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="L4" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>82.5</v>
+      <c r="N4" s="13" t="n">
+        <v>178.5</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="S4" s="8" t="n">
+      <c r="S4" s="3" t="n">
         <v>27</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>631.1</v>
+        <v>63.7</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>18.1</v>
+        <v>27.7</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
@@ -848,12 +874,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="n">
+        <v>6.6</v>
+      </c>
       <c r="D5" s="11" t="n">
         <v>24.3</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>21.5</v>
@@ -862,14 +890,12 @@
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="8" t="n">
-        <v>87.40000000000001</v>
-      </c>
+      <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>25.8</v>
+        <v>9.6</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>19.1</v>
@@ -877,37 +903,41 @@
       <c r="M5" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="N5" s="8" t="n">
-        <v>19.9</v>
+      <c r="N5" s="3" t="n">
+        <v>89.90000000000001</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Q5" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>187.8</v>
+        <v>87.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>12.9</v>
+        <v>2.7</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="n">
-        <v>27.5</v>
+      <c r="W5" s="13" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="X5" s="13" t="n">
+        <v>72.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>726.1</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>9.699999999999999</v>
@@ -926,7 +956,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>432.4</v>
+        <v>831.6</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>31.4</v>
@@ -940,60 +970,62 @@
       <c r="G6" s="11" t="n">
         <v>11.6</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="13" t="n">
         <v>17.8</v>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="3" t="n">
         <v>19</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>188.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="Q6" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q6" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="8" t="n">
-        <v>232.9</v>
+      <c r="R6" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>651.1</v>
+        <v>25.9</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>1608.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="V6" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>185</v>
+        <v>85</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1009,71 +1041,71 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1437.3</v>
-      </c>
-      <c r="D7" s="8" t="n">
+        <v>143.7</v>
+      </c>
+      <c r="D7" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>251.1</v>
-      </c>
-      <c r="G7" s="8" t="n">
+      <c r="E7" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="13" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>14.9</v>
+        <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>13.1</v>
+        <v>0</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>12.3</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="N7" s="8" t="n">
-        <v>67.3</v>
+      <c r="N7" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>187.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>31.9</v>
+        <v>21.9</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="S7" s="8" t="n">
+      <c r="S7" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>2022.1</v>
+        <v>52.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="3" t="n">
         <v>27.6</v>
       </c>
-      <c r="W7" s="8" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X7" s="8" t="n">
-        <v>27.8</v>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="13" t="n">
+        <v>26.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>177.9</v>
+        <v>1772.9</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>17.5</v>
@@ -1092,7 +1124,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1297.2</v>
+        <v>98971.60000000001</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>32.6</v>
@@ -1110,40 +1142,40 @@
         <v>17.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>16.9</v>
+        <v>1.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K8" s="8" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="L8" s="8" t="n">
+      <c r="K8" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="N8" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>187.7</v>
+        <v>87.7</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="3" t="n">
         <v>33.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>2524.1</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>11.6</v>
@@ -1154,15 +1186,13 @@
       <c r="W8" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X8" s="8" t="n">
+      <c r="X8" s="3" t="n">
         <v>27</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>90.2</v>
       </c>
-      <c r="Z8" s="3" t="n">
-        <v>2.9</v>
-      </c>
+      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1177,64 +1207,74 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1666.5</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>852.6</v>
-      </c>
-      <c r="E9" s="10" t="inlineStr"/>
-      <c r="F9" s="10" t="inlineStr"/>
-      <c r="G9" s="12" t="n">
-        <v>68.09999999999999</v>
+        <v>166.6</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>8</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>80.5</v>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="n">
+        <v>211.2</v>
+      </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>44.3</v>
+        <v>44</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>194.3</v>
+        <v>94.3</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>187.8</v>
+        <v>87.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>196.3</v>
+        <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1440.9</v>
+        <v>1840.9</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>162.9</v>
+        <v>12.9</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1138.8</v>
+        <v>138.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1617.3</v>
+        <v>1217.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>132.9</v>
+        <v>1831.9</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>1360.9</v>
+        <v>360.9</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>1126.1</v>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
+        <v>126.1</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>113</v>
+      </c>
       <c r="X9" s="3" t="inlineStr"/>
-      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="n">
+        <v>11418.4</v>
+      </c>
       <c r="Z9" s="3" t="n">
-        <v>32.8</v>
+        <v>58.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1250,39 +1290,43 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>333.3</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>185.1</v>
-      </c>
-      <c r="F10" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F10" s="11" t="n">
         <v>24.5</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>16.1</v>
+      <c r="H10" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.2</v>
+        <v>15.2</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="8" t="n">
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" s="13" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="N10" s="13" t="n">
+        <v>19.3</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>188.2</v>
+        <v>88.5</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>2.6</v>
@@ -1290,29 +1334,29 @@
       <c r="Q10" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R10" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="S10" s="8" t="n">
+      <c r="S10" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>272.2</v>
+        <v>72.2</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>0.5</v>
+        <v>25.2</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X10" s="3" t="n">
+      <c r="X10" s="13" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>180.5</v>
+        <v>80.5</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>16.6</v>
@@ -1331,7 +1375,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1445</v>
+        <v>1445.1</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>28.7</v>
@@ -1349,55 +1393,59 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>13.3</v>
+        <v>3.9</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
+        <v>80.59999999999999</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="N11" s="8" t="n">
-        <v>20.7</v>
+      <c r="N11" s="13" t="n">
+        <v>46.7</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>187.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>41.9</v>
+        <v>27.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>981.9</v>
+        <v>230.8</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="V11" s="8" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V11" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="8" t="n">
-        <v>24.7</v>
+      <c r="W11" s="3" t="n">
+        <v>4.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>30.9</v>
+        <v>31.9</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>197.5</v>
-      </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+        <v>97.5</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>10.8</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1412,10 +1460,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>383.6</v>
+        <v>318.3</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>19.6</v>
@@ -1423,23 +1471,23 @@
       <c r="F12" s="11" t="n">
         <v>23.9</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>18</v>
+      <c r="G12" s="11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>81.09999999999999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>19.3</v>
@@ -1451,10 +1499,10 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>27.8</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>27.2</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>25.2</v>
@@ -1463,25 +1511,25 @@
         <v>30.8</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>8544.1</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="V12" s="8" t="n">
+      <c r="V12" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="W12" s="8" t="n">
-        <v>284.4</v>
-      </c>
-      <c r="X12" s="8" t="n">
+      <c r="W12" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X12" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>197.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>10.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1497,13 +1545,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>39356.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>25.5</v>
@@ -1511,19 +1559,19 @@
       <c r="G13" s="11" t="n">
         <v>11.3</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>12.6</v>
+        <v>0.1</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="L13" s="8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1533,10 +1581,12 @@
         <v>20.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>189.1</v>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="8" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q13" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1548,23 +1598,23 @@
       <c r="T13" s="3" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="U13" s="8" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="V13" s="8" t="n">
+      <c r="U13" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="8" t="n">
+      <c r="W13" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="X13" s="13" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>197.7</v>
+        <v>192.9</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>10.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1580,13 +1630,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>13974</v>
+        <v>32.4</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>26.1</v>
@@ -1595,29 +1645,31 @@
         <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>1.3</v>
+      </c>
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="L14" s="8" t="n">
+      <c r="L14" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>189.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>30.6</v>
@@ -1626,7 +1678,7 @@
         <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1640,7 +1692,7 @@
       <c r="W14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="13" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
@@ -1663,13 +1715,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>433.5</v>
+        <v>1643.3</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>29.5</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>24.9</v>
@@ -1677,27 +1729,29 @@
       <c r="G15" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.9</v>
+        <v>11.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>10</v>
+        <v>0.8</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>21.3</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>188.8</v>
+        <v>88.8</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>2.6</v>
@@ -1708,26 +1762,26 @@
       <c r="R15" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="S15" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>163.8</v>
+        <v>63.8</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="V15" s="8" t="n">
+      <c r="V15" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="W15" s="8" t="n">
-        <v>241.1</v>
+      <c r="W15" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>174</v>
+        <v>1741</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>17.9</v>
@@ -1746,22 +1800,22 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>11992.8</v>
+        <v>199.2</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>99.5</v>
+        <v>150.2</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>124.7</v>
       </c>
-      <c r="G16" s="12" t="n">
-        <v>15.1</v>
+      <c r="G16" s="3" t="n">
+        <v>50.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>190.3</v>
+        <v>9</v>
       </c>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="n">
@@ -1771,42 +1825,46 @@
         <v>16</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1100.9</v>
+        <v>460.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>194.6</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>105.2</v>
+        <v>1055.9</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>444.1</v>
+        <v>4464.1</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>12.9</v>
+        <v>102.9</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1142.8</v>
+        <v>142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>123</v>
+        <v>1123</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>142.5</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>1368.7</v>
+        <v>368.7</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>533441.5</v>
+        <v>53.1</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>137.5</v>
+      </c>
       <c r="Y16" s="3" t="n">
-        <v>1455.1</v>
+        <v>455.1</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>13.4</v>
@@ -1825,7 +1883,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>39.9</v>
+        <v>5.8</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>30</v>
@@ -1836,51 +1894,47 @@
       <c r="F17" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="I17" s="8" t="n">
-        <v>81.2</v>
+      <c r="I17" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="8" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="M17" s="8" t="n">
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>20</v>
+      <c r="N17" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>188.8</v>
+        <v>88.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="8" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>946.4</v>
-      </c>
-      <c r="S17" s="8" t="n">
+      <c r="Q17" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="R17" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="S17" s="13" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>173.7</v>
-      </c>
-      <c r="U17" s="8" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="U17" s="13" t="n">
         <v>10.6</v>
       </c>
-      <c r="V17" s="8" t="n">
-        <v>24.2</v>
+      <c r="V17" s="13" t="n">
+        <v>48.2</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>23</v>
@@ -1908,68 +1962,68 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>437.5</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="8" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="I18" s="8" t="n">
-        <v>39.5</v>
+        <v>0.1</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>91</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>18</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.2</v>
+        <v>9.6</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>12.7</v>
+        <v>27.7</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>19.3</v>
+        <v>1.9</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="Q18" s="8" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Q18" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S18" s="8" t="n">
+      <c r="S18" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>163.1</v>
+        <v>6.2</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="8" t="n">
+      <c r="V18" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="X18" s="3" t="n">
-        <v>31</v>
+      <c r="X18" s="13" t="n">
+        <v>11.3</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>92.09999999999999</v>
@@ -1991,77 +2045,75 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1423.9</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E19" s="11" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="G19" s="12" t="n">
-        <v>12.5</v>
+      <c r="G19" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.1</v>
+        <v>11.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>13.5</v>
+        <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>28.5</v>
+        <v>91.5</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>20</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>2.3</v>
+        <v>87.5</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>31.8</v>
+        <v>2.8</v>
+      </c>
+      <c r="Q19" s="13" t="n">
+        <v>61.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>25.3</v>
+        <v>94.2</v>
+      </c>
+      <c r="S19" s="13" t="n">
+        <v>295.3</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>62.1</v>
+        <v>54</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="8" t="n">
-        <v>25.8</v>
+      <c r="V19" s="13" t="n">
+        <v>655.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="3" t="n">
         <v>27</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="Z19" s="3" t="n">
-        <v>16.2</v>
-      </c>
+        <v>81.8</v>
+      </c>
+      <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2076,39 +2128,37 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>256.8</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E20" s="11" t="n">
+        <v>856.8</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="E20" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="11" t="n">
-        <v>23.5</v>
+      <c r="F20" s="3" t="n">
+        <v>25.5</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <v>82.2</v>
+      <c r="H20" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>2408</v>
-      </c>
-      <c r="L20" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N20" s="8" t="n">
+      <c r="N20" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
@@ -2118,31 +2168,31 @@
         <v>12.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R20" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R20" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>70.7</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>19.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="W20" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>167.2</v>
+        <v>67.2</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>10.2</v>
@@ -2161,7 +2211,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1433.5</v>
+        <v>43.3</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>30.8</v>
@@ -2176,29 +2226,33 @@
         <v>12.4</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>17.7</v>
+        <v>1.7</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>1.4</v>
+        <v>12.3</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>186.7</v>
-      </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="8" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="R21" s="3" t="n">
@@ -2208,16 +2262,16 @@
         <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="V21" s="8" t="n">
+      <c r="V21" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>2.2</v>
+        <v>22.4</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>25.9</v>
@@ -2242,7 +2296,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>374</v>
+        <v>34.4</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>31.8</v>
@@ -2257,13 +2311,13 @@
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I22" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I22" s="13" t="n">
         <v>21.1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3.7</v>
@@ -2278,10 +2332,10 @@
         <v>17.5</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>21.6</v>
+        <v>87</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>30.2</v>
@@ -2289,29 +2343,29 @@
       <c r="R22" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="S22" s="8" t="n">
+      <c r="S22" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>156.4</v>
+        <v>56.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="8" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="X22" s="8" t="n">
+      <c r="V22" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W22" s="13" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="X22" s="13" t="n">
         <v>21.6</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>185.5</v>
+        <v>85.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2329,17 +2383,17 @@
       <c r="C23" s="3" t="n">
         <v>1925.5</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="20" t="n">
         <v>153.1</v>
       </c>
-      <c r="E23" s="11" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>122.9</v>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>16</v>
+      <c r="E23" s="20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F23" s="20" t="n">
+        <v>123</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>1602.7</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2348,44 +2402,52 @@
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>135.5</v>
+        <v>15.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>49.9</v>
+        <v>49.5</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>195.2</v>
+        <v>95.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1882.8</v>
+        <v>88.2</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>196.5</v>
+        <v>96.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1437.2</v>
+        <v>1137.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
+        <v>1535.7</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>1145.1</v>
+      </c>
       <c r="S23" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>1295.2</v>
+        <v>295.2</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>85.2</v>
       </c>
-      <c r="V23" s="3" t="inlineStr"/>
-      <c r="W23" s="3" t="inlineStr"/>
+      <c r="V23" s="3" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>210.7</v>
+      </c>
       <c r="X23" s="3" t="n">
-        <v>1126.7</v>
+        <v>226.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1411</v>
+        <v>1811</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>27.1</v>
@@ -2404,44 +2466,48 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>385.1</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E24" s="11" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="D24" s="20" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E24" s="20" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="11" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="G24" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>87.40000000000001</v>
+      <c r="F24" s="20" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>5.1</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="N24" s="8" t="n">
-        <v>19.5</v>
+      <c r="N24" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>187.4</v>
-      </c>
-      <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="8" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Q24" s="3" t="n">
         <v>29.2</v>
       </c>
       <c r="R24" s="3" t="n">
@@ -2451,23 +2517,21 @@
         <v>23.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="V24" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="V24" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="X24" s="8" t="n">
+      <c r="X24" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="Y24" s="3" t="n">
-        <v>182.2</v>
-      </c>
+      <c r="Y24" s="3" t="inlineStr"/>
       <c r="Z24" s="3" t="n">
         <v>5.4</v>
       </c>
@@ -2485,74 +2549,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1374</v>
+        <v>374</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>32.1</v>
+        <v>21.5</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>19.3</v>
+        <v>19.9</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>25.7</v>
+        <v>20.7</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>9.1</v>
+        <v>12.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>81414.60000000001</v>
+      </c>
       <c r="L25" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="N25" s="8" t="n">
+      <c r="N25" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q25" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Q25" s="3" t="n">
         <v>31.3</v>
       </c>
-      <c r="R25" s="3" t="n">
-        <v>243.1</v>
-      </c>
-      <c r="S25" s="8" t="n">
+      <c r="R25" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S25" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>956.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="V25" s="8" t="n">
-        <v>224.2</v>
-      </c>
-      <c r="W25" s="8" t="n">
+      <c r="V25" s="13" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="W25" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="13" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>1747.6</v>
+        <v>174.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>7.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2568,7 +2634,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>329.8</v>
+        <v>329.2</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>30.8</v>
@@ -2582,32 +2648,32 @@
       <c r="G26" s="11" t="n">
         <v>12.2</v>
       </c>
-      <c r="H26" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="I26" s="8" t="n">
-        <v>11.9</v>
+      <c r="H26" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N26" s="8" t="n">
-        <v>949.2</v>
+        <v>17.6</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>24.4</v>
@@ -2619,23 +2685,21 @@
         <v>24.5</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="V26" s="8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V26" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="X26" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X26" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="Y26" s="3" t="n">
-        <v>181.1</v>
-      </c>
+      <c r="Y26" s="3" t="inlineStr"/>
       <c r="Z26" s="3" t="n">
         <v>17.6</v>
       </c>
@@ -2653,16 +2717,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D27" s="11" t="n">
+        <v>952.2</v>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="E27" s="11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>23.8</v>
+      <c r="E27" s="15" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>18.8</v>
@@ -2670,50 +2734,52 @@
       <c r="H27" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="8" t="n">
-        <v>21.9</v>
+      <c r="I27" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="L27" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>187.5</v>
+        <v>82.5</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Q27" s="8" t="n">
-        <v>6</v>
+        <v>2.9</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>26</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>21.6</v>
+        <v>22.6</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>168.4</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="W27" s="8" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X27" s="8" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="U27" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W27" s="13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="X27" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y27" s="3" t="n">
@@ -2736,31 +2802,31 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>9389.299999999999</v>
-      </c>
-      <c r="D28" s="11" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="D28" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="E28" s="11" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F28" s="11" t="n">
+      <c r="E28" s="15" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>25</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K28" s="3" t="n">
         <v>19</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J28" s="8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>19.6</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.6</v>
@@ -2768,41 +2834,41 @@
       <c r="M28" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N28" s="8" t="n">
-        <v>21.3</v>
+      <c r="N28" s="13" t="n">
+        <v>281.3</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>187.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>2.9</v>
+        <v>11.4</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>23</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>164.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="V28" s="8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="V28" s="3" t="n">
         <v>26</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="X28" s="8" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="X28" s="13" t="n">
         <v>27.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>16</v>
@@ -2821,16 +2887,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>408.5</v>
-      </c>
-      <c r="D29" s="11" t="n">
+        <v>140.8</v>
+      </c>
+      <c r="D29" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="E29" s="11" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>24.9</v>
+      <c r="E29" s="15" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>22.9</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>19.1</v>
@@ -2839,7 +2905,7 @@
         <v>20.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>16.7</v>
+        <v>11.7</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.9</v>
@@ -2853,23 +2919,23 @@
       <c r="M29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="8" t="n">
+      <c r="N29" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="Q29" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q29" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="8" t="n">
-        <v>226.5</v>
+      <c r="S29" s="3" t="n">
+        <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>162.6</v>
@@ -2877,17 +2943,17 @@
       <c r="U29" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="V29" s="8" t="n">
+      <c r="V29" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="X29" s="3" t="n">
+      <c r="X29" s="13" t="n">
         <v>26.5</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>8182.8</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>16.1</v>
@@ -2906,22 +2972,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1856.4</v>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>150.3</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>124.1</v>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>15.2</v>
+        <v>11836.4</v>
+      </c>
+      <c r="D30" s="20" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="E30" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F30" s="20" t="n">
+        <v>1224.1</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>191.9</v>
+        <v>9.1</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>180</v>
@@ -2930,49 +2996,49 @@
         <v>15.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>125.4</v>
+        <v>25.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>199.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1103.2</v>
+        <v>9103.4</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>1441.9</v>
+        <v>14241.9</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>13.1</v>
+        <v>10.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1138.5</v>
+        <v>138.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1113.7</v>
+        <v>113.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>122.8</v>
+        <v>122.7</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>1332.8</v>
+        <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>164.5</v>
+        <v>16.4</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1823.1</v>
+        <v>1123.1</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>1124.3</v>
+        <v>164.3</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>1399.8</v>
+        <v>39.4</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>32.6</v>
@@ -2991,22 +3057,22 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>383.1</v>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E31" s="11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="E31" s="20" t="n">
         <v>19.6</v>
       </c>
-      <c r="F31" s="11" t="n">
-        <v>24.8</v>
+      <c r="F31" s="15" t="n">
+        <v>94.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>184.5</v>
+        <v>10.5</v>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>182.4</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2</v>
@@ -3014,52 +3080,52 @@
       <c r="J31" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
+      <c r="K31" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="13" t="n">
         <v>19.9</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>6.4</v>
+        <v>20.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>188.4</v>
+        <v>22.4</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="Q31" s="8" t="n">
+      <c r="Q31" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="S31" s="8" t="n">
-        <v>24.5</v>
+      <c r="S31" s="3" t="n">
+        <v>845.8</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>166.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="V31" s="8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V31" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="W31" s="8" t="n">
+      <c r="W31" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v>6.5</v>
-      </c>
+        <v>80.90000000000001</v>
+      </c>
+      <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3074,72 +3140,76 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>32.8</v>
+        <v>943.7</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>42.8</v>
       </c>
       <c r="E32" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="F32" s="11" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="H32" s="3" t="n">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>13.5</v>
+        <v>3.9</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="N32" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N32" s="13" t="n">
         <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>188.4</v>
-      </c>
-      <c r="P32" s="3" t="inlineStr"/>
+        <v>88.40000000000001</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="Q32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>156.6</v>
+        <v>560.6</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="X32" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V32" s="13" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="W32" s="13" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="X32" s="13" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>169.1</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>1118.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3155,38 +3225,40 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1397</v>
-      </c>
-      <c r="D33" s="11" t="n">
-        <v>33.6</v>
+        <v>397.1</v>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>38.2</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>26.8</v>
+        <v>19.8</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>65.7</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>34.1</v>
+        <v>13.9</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>17.9</v>
+        <v>12.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="3" t="n">
-        <v>10</v>
+        <v>11.4</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>1.1</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>49.5</v>
+        <v>19.5</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>26.7</v>
+        <v>21.7</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>87.40000000000001</v>
@@ -3194,32 +3266,32 @@
       <c r="P33" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q33" s="8" t="n">
+      <c r="Q33" s="3" t="n">
         <v>32.9</v>
       </c>
       <c r="R33" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="S33" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="S33" s="3" t="n">
-        <v>63.4</v>
-      </c>
       <c r="T33" s="3" t="n">
-        <v>1947.7</v>
-      </c>
-      <c r="U33" s="8" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="V33" s="8" t="n">
+      <c r="V33" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>127.6</v>
+        <v>122.6</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>17.4</v>
@@ -3238,7 +3310,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>362.4</v>
+        <v>36.2</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>30.4</v>
@@ -3253,16 +3325,16 @@
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K34" s="3" t="n">
-        <v>4.2</v>
+      <c r="K34" s="13" t="n">
+        <v>2.4</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>20.4</v>
@@ -3274,38 +3346,40 @@
         <v>21</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>187.3</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr"/>
+        <v>87.3</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="Q34" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S34" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="S34" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>7886.8</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>17.2</v>
+        <v>7.5</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>55.4</v>
+        <v>25.5</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X34" s="8" t="n">
+      <c r="X34" s="13" t="n">
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>183.2</v>
+        <v>1832.8</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3332,65 +3406,65 @@
       <c r="F35" s="11" t="n">
         <v>22.6</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>23.9</v>
+      <c r="G35" s="11" t="n">
+        <v>3.9</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18.7</v>
+        <v>1.8</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L35" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <v>9.300000000000001</v>
+      <c r="N35" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>854.1</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Q35" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q35" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S35" s="8" t="n">
+      <c r="S35" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>88.5</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V35" s="8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="X35" s="8" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X35" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>188.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>2.9</v>
+        <v>12.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3409,15 +3483,15 @@
         <v>398.9</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>28.6</v>
+        <v>38.6</v>
       </c>
       <c r="E36" s="11" t="n">
         <v>20</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="G36" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="G36" s="11" t="n">
         <v>18.6</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3427,10 +3501,10 @@
         <v>2.2</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>20.6</v>
@@ -3438,45 +3512,43 @@
       <c r="M36" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="N36" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="8" t="n">
+      <c r="Q36" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="R36" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S36" s="8" t="n">
-        <v>593.8</v>
+      <c r="S36" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>72.3</v>
+        <v>822.5</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="W36" s="8" t="n">
+      <c r="V36" s="13" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="W36" s="13" t="n">
         <v>22.1</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>24.8</v>
+      <c r="X36" s="13" t="n">
+        <v>46.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>178.2</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>16.9</v>
-      </c>
+        <v>78.2</v>
+      </c>
+      <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3493,20 +3565,20 @@
       <c r="C37" s="3" t="n">
         <v>11683.5</v>
       </c>
-      <c r="D37" s="11" t="n">
-        <v>150.1</v>
+      <c r="D37" s="20" t="n">
+        <v>1450.1</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="F37" s="11" t="n">
+        <v>101</v>
+      </c>
+      <c r="F37" s="20" t="n">
         <v>125.5</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>192.4</v>
+        <v>9224.1</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
@@ -3515,44 +3587,52 @@
         <v>15.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>160.8</v>
+        <v>10.2</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="n">
+        <v>1396.5</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>127.2</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>1432.5</v>
+        <v>437.5</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>139.6</v>
+        <v>129</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>126.8</v>
+        <v>126</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3431.1</v>
+        <v>343.7</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>165.7</v>
+        <v>65.7</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="3" t="inlineStr"/>
-      <c r="X37" s="3" t="inlineStr"/>
+      <c r="W37" s="3" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>127.1</v>
+      </c>
       <c r="Y37" s="3" t="n">
         <v>396.6</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>342.4</v>
+        <v>34.4</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3570,28 +3650,30 @@
       <c r="C38" s="3" t="n">
         <v>336.7</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D38" s="20" t="n">
         <v>30</v>
       </c>
       <c r="E38" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F38" s="20" t="n">
         <v>25.1</v>
       </c>
       <c r="G38" s="11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>18.5</v>
+        <v>88.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J38" s="8" t="n">
-        <v>211.1</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
@@ -3599,13 +3681,13 @@
         <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>21.4</v>
+        <v>28.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>187.5</v>
+        <v>87.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>27.9</v>
@@ -3613,29 +3695,29 @@
       <c r="R38" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>25.2</v>
+      <c r="S38" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>168.7</v>
+        <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>18.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>22.4</v>
+        <v>224.2</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>79.3</v>
+        <v>179.3</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>18.9</v>
+        <v>16.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3651,76 +3733,74 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1400.8</v>
+        <v>14001.8</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>31.9</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G39" s="11" t="n">
-        <v>12.3</v>
+        <v>25.7</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>28</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="I39" s="3" t="n">
-        <v>52.5</v>
-      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
-        <v>3.9</v>
+        <v>29.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>20.5</v>
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>10.5</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="8" t="n">
-        <v>22</v>
+      <c r="N39" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="P39" s="8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="Q39" s="8" t="n">
+      <c r="P39" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>23.1</v>
+        <v>25.1</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>345.1</v>
+        <v>534.5</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="8" t="n">
+      <c r="V39" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="W39" s="8" t="n">
+      <c r="W39" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X39" s="8" t="n">
-        <v>27.6</v>
+      <c r="X39" s="3" t="n">
+        <v>97.59999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>175.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>17.6</v>
+        <v>13.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3738,29 +3818,29 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="E40" s="11" t="n">
-        <v>20.2</v>
+      <c r="D40" s="15" t="n">
+        <v>44.46</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>90.2</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H40" s="8" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>14.9</v>
+        <v>4.9</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>20.4</v>
@@ -3768,16 +3848,16 @@
       <c r="M40" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="N40" s="8" t="n">
-        <v>10.1</v>
+      <c r="N40" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>88</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Q40" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>21</v>
       </c>
       <c r="R40" s="3" t="n">
@@ -3787,25 +3867,25 @@
         <v>22.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>189.7</v>
+        <v>89.7</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="X40" s="8" t="n">
-        <v>21.7</v>
+        <v>28.3</v>
+      </c>
+      <c r="W40" s="13" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="X40" s="13" t="n">
+        <v>217.2</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>85.5</v>
+        <v>181.5</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>5.7</v>
+        <v>19.9</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3821,33 +3901,33 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1448.8</v>
-      </c>
-      <c r="D41" s="11" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>19.6</v>
+        <v>114.8</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>24.4</v>
+        <v>34.5</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="H41" s="13" t="n">
         <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L41" s="8" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L41" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="M41" s="3" t="n">
@@ -3865,26 +3945,26 @@
       <c r="Q41" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="8" t="n">
+      <c r="R41" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>584.5</v>
+        <v>58.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>4.6</v>
+        <v>24.6</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="X41" s="8" t="n">
-        <v>25.2</v>
+      <c r="X41" s="13" t="n">
+        <v>25.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>174</v>
@@ -3906,7 +3986,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>464.3</v>
+        <v>86.2</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>32.8</v>
@@ -3917,32 +3997,32 @@
       <c r="F42" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G42" s="8" t="n">
+      <c r="G42" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>20.1</v>
+        <v>0.8</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L42" s="8" t="n">
-        <v>72.8</v>
+        <v>0.2</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>16.8</v>
+        <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>289</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>12.1</v>
@@ -3953,29 +4033,29 @@
       <c r="R42" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="S42" s="8" t="n">
+      <c r="S42" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v>22.2</v>
+        <v>50</v>
+      </c>
+      <c r="U42" s="13" t="n">
+        <v>28.2</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>0.2</v>
+        <v>25.8</v>
+      </c>
+      <c r="X42" s="13" t="n">
+        <v>10.4</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>87</v>
+        <v>18708</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>3.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3991,7 +4071,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2341.3</v>
+        <v>44.1</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>32</v>
@@ -4005,14 +4085,14 @@
       <c r="G43" s="11" t="n">
         <v>13.4</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>24.9</v>
+        <v>2.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>15.2</v>
@@ -4030,37 +4110,35 @@
         <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q43" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="8" t="n">
+      <c r="R43" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>181.4</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="V43" s="8" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="W43" s="8" t="n">
-        <v>791.4</v>
+      <c r="W43" s="3" t="n">
+        <v>22.4</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="Y43" s="3" t="n">
         <v>182.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4076,13 +4154,13 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>141.6</v>
+        <v>121.6</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="F44" s="11" t="n">
         <v>21.4</v>
@@ -4093,8 +4171,8 @@
       <c r="H44" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>10.8</v>
+      <c r="I44" s="13" t="n">
+        <v>80.8</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>0.6</v>
@@ -4106,34 +4184,34 @@
         <v>19.4</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>6.5</v>
+        <v>19.9</v>
+      </c>
+      <c r="N44" s="13" t="n">
+        <v>0.8</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>390.1</v>
+        <v>189</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="Q44" s="8" t="n">
-        <v>28.6</v>
+      <c r="Q44" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>181</v>
+        <v>181.9</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>22.3</v>
+        <v>15.9</v>
+      </c>
+      <c r="V44" s="13" t="n">
+        <v>822.3</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>20.2</v>
@@ -4155,58 +4233,66 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>16871.1</v>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>174</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>114</v>
+        <v>18841.1</v>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>841.1</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>122.2</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>143.7</v>
-      </c>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr"/>
+        <v>153.9</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>105.6</v>
+      </c>
       <c r="I45" s="3" t="n">
-        <v>123.3</v>
+        <v>169</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>116.6</v>
+        <v>16.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>30</v>
+        <v>2816.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>110.4</v>
+        <v>12180.4</v>
       </c>
       <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="n">
+        <v>110109210619.1</v>
+      </c>
       <c r="O45" s="3" t="n">
-        <v>10234.2</v>
+        <v>204.1</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1167.4</v>
+        <v>16808.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1691.2</v>
+        <v>1257.2</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>129.7</v>
+        <v>1291.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>26.2</v>
+        <v>18317.9</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>4084.4</v>
+        <v>44841.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>112.2</v>
+        <v>81.5</v>
       </c>
       <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="n">
+        <v>1122.2</v>
+      </c>
       <c r="X45" s="3" t="n">
-        <v>184832438.2</v>
+        <v>924.7</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>81.5</v>
@@ -4228,30 +4314,32 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>311.7</v>
-      </c>
-      <c r="D46" s="11" t="n">
+        <v>511.7</v>
+      </c>
+      <c r="D46" s="20" t="n">
         <v>29.1</v>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="20" t="n">
         <v>18.9</v>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="11" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H46" s="8" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>2.2</v>
+      <c r="G46" s="13" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="H46" s="13" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I46" s="13" t="n">
+        <v>122.6</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
       </c>
@@ -4259,7 +4347,7 @@
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>20.2</v>
+        <v>60.5</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>89</v>
@@ -4267,33 +4355,31 @@
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="R46" s="8" t="n">
+      <c r="Q46" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R46" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="8" t="n">
+      <c r="V46" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="8" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>81.5</v>
-      </c>
+      <c r="W46" s="13" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X46" s="13" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,14 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,43 +140,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -798,20 +780,20 @@
       <c r="C4" s="3" t="n">
         <v>83.7</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="9" t="n">
         <v>31.2</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="9" t="n">
         <v>14</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>91241.10000000001</v>
+        <v>91124.10000000001</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
@@ -820,16 +802,16 @@
         <v>4.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>17.6</v>
+        <v>88.8</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>75.59999999999999</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="N4" s="13" t="n">
-        <v>178.5</v>
+      <c r="N4" s="3" t="n">
+        <v>17.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -853,7 +835,7 @@
         <v>15.4</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>27.7</v>
+        <v>27.2</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24</v>
@@ -877,26 +859,24 @@
       <c r="C5" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="D5" s="11" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E5" s="11" t="n">
+      <c r="D5" s="9" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="9" t="n">
         <v>21.5</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="9" t="n">
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="n">
         <v>19.1</v>
       </c>
@@ -904,14 +884,12 @@
         <v>18</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="P5" s="3" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
         <v>20.5</v>
       </c>
@@ -925,19 +903,19 @@
         <v>87.8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W5" s="13" t="n">
+      <c r="W5" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="X5" s="13" t="n">
-        <v>72.5</v>
+      <c r="X5" s="3" t="n">
+        <v>27.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>726.1</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>9.699999999999999</v>
@@ -956,31 +934,31 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>831.6</v>
-      </c>
-      <c r="D6" s="11" t="n">
+        <v>432.6</v>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="9" t="n">
         <v>11.6</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20.3</v>
@@ -1007,10 +985,10 @@
         <v>25.9</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1.6</v>
+        <v>18.6</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>26.2</v>
@@ -1041,25 +1019,25 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>143.7</v>
-      </c>
-      <c r="D7" s="11" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>14.8</v>
+      <c r="G7" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>84.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>18.2</v>
+        <v>2.2</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>4.9</v>
@@ -1067,17 +1045,17 @@
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="13" t="n">
+      <c r="L7" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="M7" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>17.3</v>
+      <c r="M7" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>27.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
@@ -1101,11 +1079,11 @@
         <v>27.6</v>
       </c>
       <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="13" t="n">
+      <c r="X7" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1772.9</v>
+        <v>727.9</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>17.5</v>
@@ -1124,18 +1102,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>98971.60000000001</v>
-      </c>
-      <c r="D8" s="11" t="n">
+        <v>297.6</v>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>32.6</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="9" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1154,7 +1132,7 @@
         <v>20</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20.5</v>
@@ -1209,13 +1187,13 @@
       <c r="C9" s="3" t="n">
         <v>166.6</v>
       </c>
-      <c r="D9" s="11" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="E9" s="11" t="n">
+      <c r="D9" s="9" t="n">
+        <v>152.6</v>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>92.5</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="9" t="n">
         <v>122.5</v>
       </c>
       <c r="G9" s="3" t="n">
@@ -1225,7 +1203,7 @@
         <v>80.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>211.2</v>
+        <v>22.2</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
@@ -1243,7 +1221,7 @@
         <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1840.9</v>
+        <v>440.9</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>12.9</v>
@@ -1252,10 +1230,10 @@
         <v>138.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1217.3</v>
+        <v>117.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1831.9</v>
+        <v>1231.9</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>360.9</v>
@@ -1269,12 +1247,14 @@
       <c r="W9" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="X9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="Y9" s="3" t="n">
-        <v>11418.4</v>
+        <v>114102.4</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>58.8</v>
+        <v>38.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1292,41 +1272,37 @@
       <c r="C10" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="9" t="n">
         <v>30.5</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="9" t="n">
         <v>24.5</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="9" t="n">
         <v>12</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>15.2</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>6.2</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="13" t="n">
+      <c r="M10" s="8" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="N10" s="13" t="n">
+      <c r="N10" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>88.5</v>
+        <v>88.2</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>2.6</v>
@@ -1352,14 +1328,14 @@
       <c r="W10" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X10" s="13" t="n">
+      <c r="X10" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>80.5</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1375,31 +1351,31 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1445.1</v>
-      </c>
-      <c r="D11" s="11" t="n">
+        <v>2445.1</v>
+      </c>
+      <c r="D11" s="9" t="n">
         <v>28.7</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>18.2</v>
+      <c r="H11" s="8" t="n">
+        <v>85.2</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>20.1</v>
@@ -1407,35 +1383,35 @@
       <c r="M11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="N11" s="13" t="n">
-        <v>46.7</v>
+      <c r="N11" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>230.8</v>
+        <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>5.7</v>
+        <v>58.7</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>25</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>4.1</v>
+        <v>2471.6</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>31.9</v>
@@ -1444,7 +1420,7 @@
         <v>97.5</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1460,22 +1436,22 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>318.3</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E12" s="11" t="n">
+        <v>383.3</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="H12" s="13" t="n">
-        <v>81.09999999999999</v>
+      <c r="H12" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.9</v>
@@ -1484,7 +1460,7 @@
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>20.6</v>
@@ -1526,10 +1502,10 @@
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>197.7</v>
+        <v>97.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>19.7</v>
+        <v>0.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1545,18 +1521,18 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F13" s="11" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F13" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="9" t="n">
         <v>11.3</v>
       </c>
       <c r="H13" s="3" t="n">
@@ -1566,10 +1542,10 @@
         <v>1.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>5.3</v>
+        <v>0.3</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>20</v>
@@ -1607,11 +1583,11 @@
       <c r="W13" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X13" s="13" t="n">
+      <c r="X13" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>192.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.2</v>
@@ -1632,27 +1608,25 @@
       <c r="C14" s="3" t="n">
         <v>32.4</v>
       </c>
-      <c r="D14" s="11" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F14" s="11" t="n">
+      <c r="D14" s="9" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F14" s="9" t="n">
         <v>26.1</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="9" t="n">
         <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
@@ -1660,7 +1634,7 @@
         <v>19.8</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.7</v>
+        <v>28.7</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>20.8</v>
@@ -1669,7 +1643,7 @@
         <v>89.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>30.6</v>
@@ -1678,7 +1652,7 @@
         <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>50.9</v>
@@ -1692,11 +1666,11 @@
       <c r="W14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="13" t="n">
+      <c r="X14" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>193</v>
+        <v>93</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>1.8</v>
@@ -1715,31 +1689,31 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1643.3</v>
-      </c>
-      <c r="D15" s="11" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D15" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F15" s="11" t="n">
+      <c r="E15" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F15" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>19.3</v>
+      <c r="G15" s="9" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>19.8</v>
+        <v>89.8</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.8</v>
+        <v>16.8</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>20.4</v>
@@ -1769,7 +1743,7 @@
         <v>63.8</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>14.1</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>24.5</v>
@@ -1781,7 +1755,7 @@
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>1741</v>
+        <v>74</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>17.9</v>
@@ -1802,13 +1776,13 @@
       <c r="C16" s="3" t="n">
         <v>199.2</v>
       </c>
-      <c r="D16" s="11" t="n">
-        <v>150.2</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="F16" s="11" t="n">
+      <c r="D16" s="9" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="F16" s="9" t="n">
         <v>124.7</v>
       </c>
       <c r="G16" s="3" t="n">
@@ -1817,7 +1791,9 @@
       <c r="H16" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="n">
+        <v>8.1</v>
+      </c>
       <c r="J16" s="3" t="n">
         <v>15.8</v>
       </c>
@@ -1825,25 +1801,25 @@
         <v>16</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>460.9</v>
+        <v>11.2</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>194.6</v>
+        <v>924.6</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1055.9</v>
+        <v>105.8</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4464.1</v>
+        <v>444.8</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>102.9</v>
+        <v>12.9</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1123</v>
+        <v>23</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>142.5</v>
@@ -1883,29 +1859,33 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D17" s="11" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="D17" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
+      <c r="G17" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="H17" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>18.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="M17" s="3" t="n">
         <v>18.9</v>
       </c>
@@ -1913,7 +1893,7 @@
         <v>21</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>88.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.6</v>
@@ -1921,32 +1901,32 @@
       <c r="Q17" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R17" s="13" t="n">
-        <v>82</v>
-      </c>
-      <c r="S17" s="13" t="n">
+      <c r="R17" s="8" t="n">
+        <v>8224</v>
+      </c>
+      <c r="S17" s="8" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="U17" s="13" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V17" s="13" t="n">
-        <v>48.2</v>
+      <c r="V17" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>12.7</v>
+        <v>2.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1962,32 +1942,34 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D18" s="15" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>91</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>34.41</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="n">
-        <v>1.5</v>
+        <v>24.9</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>9.6</v>
+        <v>19.6</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>27.7</v>
@@ -1996,10 +1978,10 @@
         <v>1.9</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>87.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>28.6</v>
@@ -2011,19 +1993,19 @@
         <v>24.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="13" t="n">
+      <c r="V18" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X18" s="13" t="n">
-        <v>11.3</v>
+      <c r="W18" s="8" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>41</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>92.09999999999999</v>
@@ -2045,19 +2027,19 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E19" s="3" t="n">
+        <v>433.6</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>18.4</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>18.8</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>11.6</v>
@@ -2066,7 +2048,7 @@
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>91.5</v>
@@ -2086,14 +2068,14 @@
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="13" t="n">
-        <v>61.8</v>
+      <c r="Q19" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="S19" s="13" t="n">
-        <v>295.3</v>
+        <v>24.2</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>54</v>
@@ -2101,8 +2083,8 @@
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="13" t="n">
-        <v>655.8</v>
+      <c r="V19" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>23.3</v>
@@ -2111,7 +2093,7 @@
         <v>27</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>81.8</v>
+        <v>81.2</v>
       </c>
       <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -2128,30 +2110,30 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>856.8</v>
-      </c>
-      <c r="D20" s="15" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="E20" s="3" t="n">
+        <v>956.8</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E20" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>25.5</v>
+      <c r="F20" s="9" t="n">
+        <v>23.5</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>18.5</v>
+        <v>1.8</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J20" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="n">
+        <v>24.3</v>
+      </c>
       <c r="L20" s="3" t="n">
         <v>20</v>
       </c>
@@ -2162,22 +2144,22 @@
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>189</v>
+        <v>289</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>70.7</v>
+        <v>707.2</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>95.09999999999999</v>
@@ -2186,7 +2168,7 @@
         <v>24.9</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>20.5</v>
+        <v>106.1</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>21.2</v>
@@ -2213,16 +2195,16 @@
       <c r="C21" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="9" t="n">
         <v>30.8</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G21" s="9" t="n">
         <v>12.4</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2235,7 +2217,7 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
@@ -2264,8 +2246,8 @@
       <c r="T21" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="U21" s="3" t="n">
-        <v>20.9</v>
+      <c r="U21" s="8" t="n">
+        <v>8.9</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.3</v>
@@ -2277,7 +2259,7 @@
         <v>25.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>185</v>
+        <v>850.8</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>14.5</v>
@@ -2296,25 +2278,25 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>374.1</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="11" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F22" s="11" t="n">
+      <c r="E22" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F22" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="G22" s="11" t="n">
-        <v>14.6</v>
+      <c r="G22" s="8" t="n">
+        <v>84.59999999999999</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I22" s="13" t="n">
-        <v>21.1</v>
+      <c r="I22" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.5</v>
@@ -2353,19 +2335,19 @@
         <v>18.7</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W22" s="13" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="X22" s="13" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="X22" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>85.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2383,17 +2365,17 @@
       <c r="C23" s="3" t="n">
         <v>1925.5</v>
       </c>
-      <c r="D23" s="20" t="n">
-        <v>153.1</v>
-      </c>
-      <c r="E23" s="20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="F23" s="20" t="n">
+      <c r="D23" s="16" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F23" s="16" t="n">
         <v>123</v>
       </c>
-      <c r="G23" s="15" t="n">
-        <v>1602.7</v>
+      <c r="G23" s="9" t="n">
+        <v>60.6</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2405,7 +2387,7 @@
         <v>15.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>49.5</v>
+        <v>495.3</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>95.2</v>
@@ -2417,16 +2399,16 @@
         <v>96.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1137.2</v>
+        <v>437.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1535.7</v>
+        <v>113.7</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>146.2</v>
+        <v>14.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1145.1</v>
+        <v>1143.1</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>19</v>
@@ -2438,16 +2420,16 @@
         <v>85.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>122.2</v>
+        <v>22.2</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>210.7</v>
+        <v>21</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>226.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1811</v>
+        <v>1411</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>27.1</v>
@@ -2466,28 +2448,28 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="D24" s="20" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="E24" s="20" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E24" s="16" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="20" t="n">
-        <v>34.6</v>
+      <c r="F24" s="16" t="n">
+        <v>32.6</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>11.2</v>
+        <v>1.7</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>0.1</v>
@@ -2499,16 +2481,16 @@
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>29.3</v>
+        <v>19.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>21.7</v>
+        <v>2.7</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>29.2</v>
+        <v>2.9</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>22.9</v>
@@ -2551,20 +2533,20 @@
       <c r="C25" s="3" t="n">
         <v>374</v>
       </c>
-      <c r="D25" s="11" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="G25" s="3" t="n">
+      <c r="D25" s="9" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G25" s="9" t="n">
         <v>12.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2.4</v>
@@ -2573,7 +2555,7 @@
         <v>3.6</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>81414.60000000001</v>
+        <v>1.6</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>19.5</v>
@@ -2585,40 +2567,40 @@
         <v>20.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>18.2</v>
+        <v>12.2</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="R25" s="13" t="n">
-        <v>4</v>
+        <v>31.5</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>24</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>56.9</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V25" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="13" t="n">
+      <c r="X25" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>174.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2636,16 +2618,16 @@
       <c r="C26" s="3" t="n">
         <v>329.2</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="9" t="n">
         <v>30.8</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="G26" s="9" t="n">
         <v>12.2</v>
       </c>
       <c r="H26" s="3" t="n">
@@ -2654,8 +2636,8 @@
       <c r="I26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>12.6</v>
+      <c r="J26" s="8" t="n">
+        <v>25.6</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.3</v>
@@ -2667,7 +2649,7 @@
         <v>17.6</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>19.2</v>
+        <v>89.2</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>87</v>
@@ -2682,13 +2664,13 @@
         <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>24.2</v>
@@ -2717,25 +2699,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>952.2</v>
-      </c>
-      <c r="D27" s="3" t="n">
+        <v>354.8</v>
+      </c>
+      <c r="D27" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="E27" s="15" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>25.8</v>
+      <c r="E27" s="9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>11.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>2.9</v>
@@ -2753,7 +2735,7 @@
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>82.5</v>
+        <v>87.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>2.9</v>
@@ -2762,7 +2744,7 @@
         <v>26</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.6</v>
+        <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23</v>
@@ -2770,20 +2752,20 @@
       <c r="T27" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U27" s="13" t="n">
-        <v>0.6</v>
+      <c r="U27" s="3" t="n">
+        <v>10.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W27" s="13" t="n">
-        <v>9.800000000000001</v>
+        <v>63.4</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>180.8</v>
+        <v>84.8</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>5.4</v>
@@ -2802,25 +2784,25 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>288.9</v>
-      </c>
-      <c r="D28" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D28" s="9" t="n">
         <v>29.8</v>
       </c>
-      <c r="E28" s="15" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="F28" s="3" t="n">
+      <c r="E28" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>19.6</v>
+      <c r="G28" s="9" t="n">
+        <v>9.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.8</v>
@@ -2834,14 +2816,14 @@
       <c r="M28" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N28" s="13" t="n">
-        <v>281.3</v>
+      <c r="N28" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>11.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>28.2</v>
@@ -2856,19 +2838,19 @@
         <v>64.90000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>26</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="X28" s="13" t="n">
+        <v>956.1</v>
+      </c>
+      <c r="X28" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>16</v>
@@ -2887,19 +2869,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>140.8</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>50.31</v>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>22.9</v>
+        <v>20.8</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>20.1</v>
@@ -2920,13 +2902,13 @@
         <v>19.2</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
@@ -2934,11 +2916,11 @@
       <c r="R29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="3" t="n">
+      <c r="S29" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>162.6</v>
+        <v>62.4</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>14.6</v>
@@ -2949,14 +2931,14 @@
       <c r="W29" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="X29" s="13" t="n">
+      <c r="X29" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>8182.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2972,25 +2954,25 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11836.4</v>
-      </c>
-      <c r="D30" s="20" t="n">
+        <v>11856.4</v>
+      </c>
+      <c r="D30" s="9" t="n">
         <v>150.5</v>
       </c>
-      <c r="E30" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F30" s="20" t="n">
-        <v>1224.1</v>
-      </c>
-      <c r="G30" s="3" t="n">
+      <c r="E30" s="9" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="G30" s="9" t="n">
         <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>9.1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>15.8</v>
@@ -2999,22 +2981,22 @@
         <v>25.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>929.6</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>9103.4</v>
+        <v>103.4</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>14241.9</v>
+        <v>441.9</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>10.1</v>
+        <v>13.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>138.5</v>
+        <v>238.5</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>113.7</v>
@@ -3026,19 +3008,19 @@
         <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>16.4</v>
+        <v>6.4</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1123.1</v>
+        <v>123.1</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>164.3</v>
+        <v>61.3</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>39.4</v>
+        <v>43.9</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>32.6</v>
@@ -3057,22 +3039,22 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="D31" s="20" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="E31" s="20" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E31" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="F31" s="15" t="n">
-        <v>94.8</v>
+      <c r="F31" s="9" t="n">
+        <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H31" s="13" t="n">
-        <v>182.4</v>
+      <c r="H31" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2</v>
@@ -3080,10 +3062,8 @@
       <c r="J31" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L31" s="13" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="M31" s="3" t="n">
@@ -3093,10 +3073,10 @@
         <v>20.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>22.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>27.7</v>
@@ -3105,25 +3085,25 @@
         <v>22.7</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>845.8</v>
+        <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>66.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>24.6</v>
+        <v>1.2</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>824.6</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -3140,16 +3120,16 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>943.7</v>
-      </c>
-      <c r="D32" s="15" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="E32" s="11" t="n">
+        <v>143.7</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="E32" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>26.9</v>
+      <c r="F32" s="9" t="n">
+        <v>28.9</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>12.6</v>
@@ -3158,13 +3138,13 @@
         <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>20.6</v>
@@ -3172,14 +3152,14 @@
       <c r="M32" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N32" s="13" t="n">
-        <v>21.5</v>
+      <c r="N32" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>31</v>
@@ -3191,25 +3171,25 @@
         <v>25.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>560.6</v>
+        <v>56.6</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="V32" s="13" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="W32" s="13" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="X32" s="13" t="n">
+      <c r="V32" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X32" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>169.1</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>11.8</v>
+        <v>111.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3225,31 +3205,31 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>397.1</v>
-      </c>
-      <c r="D33" s="15" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="E33" s="11" t="n">
+        <v>310.1</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F33" s="15" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="G33" s="3" t="n">
+      <c r="F33" s="9" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G33" s="9" t="n">
         <v>13.9</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>12.9</v>
+        <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>11.4</v>
+        <v>4.4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K33" s="13" t="n">
-        <v>1.1</v>
+      <c r="K33" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.9</v>
@@ -3269,8 +3249,8 @@
       <c r="Q33" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>29.9</v>
+      <c r="R33" s="8" t="n">
+        <v>38.9</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>23.9</v>
@@ -3291,10 +3271,10 @@
         <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>122.6</v>
+        <v>1727.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3312,16 +3292,16 @@
       <c r="C34" s="3" t="n">
         <v>36.2</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="9" t="n">
         <v>30.4</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="G34" s="9" t="n">
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3333,8 +3313,8 @@
       <c r="J34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K34" s="13" t="n">
-        <v>2.4</v>
+      <c r="K34" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>20.4</v>
@@ -3355,28 +3335,28 @@
         <v>26.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>28.2</v>
+        <v>23.2</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>7886.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V34" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V34" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="X34" s="13" t="n">
+      <c r="X34" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>1832.8</v>
+        <v>182.8</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>5.4</v>
@@ -3395,18 +3375,18 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>187.9</v>
-      </c>
-      <c r="D35" s="11" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="D35" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="G35" s="9" t="n">
         <v>3.9</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3428,10 +3408,10 @@
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>21.3</v>
+        <v>29.3</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>3.6</v>
@@ -3449,22 +3429,22 @@
         <v>88.5</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>7.1</v>
+        <v>28.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>21.6</v>
+        <v>28.6</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>26.3</v>
+        <v>20.3</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>188.5</v>
+        <v>88.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3482,20 +3462,20 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="11" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="E36" s="11" t="n">
+      <c r="D36" s="9" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="F36" s="11" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="G36" s="11" t="n">
-        <v>18.6</v>
+      <c r="F36" s="9" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>8.6</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>19</v>
+        <v>190.1</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>2.2</v>
@@ -3504,7 +3484,7 @@
         <v>12.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>20.6</v>
@@ -3513,7 +3493,7 @@
         <v>19.4</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>89</v>
@@ -3531,19 +3511,19 @@
         <v>25.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>822.5</v>
+        <v>72.3</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="13" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="W36" s="13" t="n">
+      <c r="V36" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="W36" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="X36" s="13" t="n">
-        <v>46.8</v>
+      <c r="X36" s="3" t="n">
+        <v>84.8</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>78.2</v>
@@ -3565,20 +3545,20 @@
       <c r="C37" s="3" t="n">
         <v>11683.5</v>
       </c>
-      <c r="D37" s="20" t="n">
-        <v>1450.1</v>
-      </c>
-      <c r="E37" s="11" t="n">
+      <c r="D37" s="9" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>101</v>
       </c>
-      <c r="F37" s="20" t="n">
-        <v>125.5</v>
+      <c r="F37" s="9" t="n">
+        <v>127.8</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>9224.1</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>12.6</v>
@@ -3593,10 +3573,10 @@
         <v>103.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1396.5</v>
+        <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>127.2</v>
+        <v>18.7</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>437.5</v>
@@ -3605,13 +3585,13 @@
         <v>14.9</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>129</v>
+        <v>139.6</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>126</v>
+        <v>1256</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>343.7</v>
@@ -3650,29 +3630,29 @@
       <c r="C38" s="3" t="n">
         <v>336.7</v>
       </c>
-      <c r="D38" s="20" t="n">
+      <c r="D38" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="20" t="n">
+      <c r="F38" s="16" t="n">
         <v>25.1</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="G38" s="9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>88.5</v>
+        <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>18.4</v>
+        <v>0.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
@@ -3696,25 +3676,25 @@
         <v>23.1</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>28.1</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>224.2</v>
+        <v>224.1</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>179.3</v>
+        <v>79.3</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>16.9</v>
@@ -3733,56 +3713,56 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>14001.8</v>
-      </c>
-      <c r="D39" s="11" t="n">
+        <v>400.8</v>
+      </c>
+      <c r="D39" s="9" t="n">
         <v>31.9</v>
       </c>
-      <c r="E39" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G39" s="13" t="n">
-        <v>28</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>18.1</v>
+      <c r="E39" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
-        <v>29.9</v>
+        <v>13.9</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>10.5</v>
+        <v>20.5</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>12.8</v>
+      <c r="N39" s="8" t="n">
+        <v>88.40000000000001</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>30.4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>25.1</v>
+        <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>23.6</v>
+        <v>22.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>534.5</v>
+        <v>54.5</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19.8</v>
@@ -3794,13 +3774,13 @@
         <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>175.4</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3818,20 +3798,20 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="15" t="n">
-        <v>44.46</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="F40" s="11" t="n">
+      <c r="D40" s="9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F40" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>19</v>
+        <v>3.9</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>89</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.4</v>
@@ -3872,20 +3852,20 @@
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="W40" s="13" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="X40" s="13" t="n">
-        <v>217.2</v>
+      <c r="V40" s="8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W40" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>21.7</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>181.5</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>19.9</v>
+        <v>15.9</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3901,31 +3881,31 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="D41" s="15" t="n">
-        <v>49.43</v>
-      </c>
-      <c r="E41" s="3" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="F41" s="11" t="n">
-        <v>34.5</v>
+      <c r="F41" s="9" t="n">
+        <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="H41" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="K41" s="13" t="n">
-        <v>11.6</v>
+        <v>3.8</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.9</v>
@@ -3963,11 +3943,11 @@
       <c r="W41" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="X41" s="13" t="n">
-        <v>25.8</v>
+      <c r="X41" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>19.6</v>
@@ -3986,15 +3966,15 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="D42" s="11" t="n">
+        <v>1464.5</v>
+      </c>
+      <c r="D42" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="E42" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="F42" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="G42" s="3" t="n">
@@ -4007,7 +3987,7 @@
         <v>4.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0.2</v>
@@ -4033,14 +4013,14 @@
       <c r="R42" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>22.2</v>
+      <c r="S42" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="U42" s="13" t="n">
-        <v>28.2</v>
+      <c r="U42" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>27.5</v>
@@ -4048,11 +4028,11 @@
       <c r="W42" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="X42" s="13" t="n">
-        <v>10.4</v>
+      <c r="X42" s="3" t="n">
+        <v>94.40000000000001</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>18708</v>
+        <v>182</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>8.699999999999999</v>
@@ -4071,18 +4051,18 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="D43" s="11" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="D43" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="G43" s="9" t="n">
         <v>13.4</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4092,7 +4072,7 @@
         <v>2.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>15.2</v>
@@ -4110,7 +4090,7 @@
         <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
@@ -4124,7 +4104,9 @@
       <c r="T43" s="3" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="U43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="V43" s="3" t="n">
         <v>23</v>
       </c>
@@ -4132,7 +4114,7 @@
         <v>22.4</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>0.3</v>
+        <v>53.1</v>
       </c>
       <c r="Y43" s="3" t="n">
         <v>182.8</v>
@@ -4154,28 +4136,28 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>121.6</v>
-      </c>
-      <c r="D44" s="11" t="n">
+        <v>141.6</v>
+      </c>
+      <c r="D44" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="E44" s="11" t="n">
+      <c r="E44" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="F44" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="G44" s="11" t="n">
+      <c r="G44" s="9" t="n">
         <v>4.9</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I44" s="13" t="n">
-        <v>80.8</v>
+      <c r="I44" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>19.7</v>
@@ -4183,39 +4165,37 @@
       <c r="L44" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="N44" s="13" t="n">
-        <v>0.8</v>
+      <c r="M44" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>189</v>
+        <v>890.1</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>181.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V44" s="13" t="n">
-        <v>822.3</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>20.2</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="W44" s="3" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4233,72 +4213,74 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>18841.1</v>
-      </c>
-      <c r="D45" s="20" t="n">
-        <v>841.1</v>
-      </c>
-      <c r="E45" s="20" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>153.9</v>
-      </c>
-      <c r="G45" s="15" t="n">
-        <v>16</v>
+        <v>168211.1</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>174.6</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>143.8</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>105.6</v>
+        <v>2637</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>169</v>
+        <v>183.3</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>2816.1</v>
+        <v>28</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>12180.4</v>
+        <v>1910.4</v>
       </c>
       <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="3" t="n">
-        <v>110109210619.1</v>
+        <v>10092105.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>204.1</v>
+        <v>34.2</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>16808.4</v>
+        <v>140.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1257.2</v>
+        <v>257.5</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1291.7</v>
+        <v>129.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>18317.9</v>
+        <v>1382</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>44841.4</v>
+        <v>484</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="V45" s="3" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="W45" s="3" t="n">
-        <v>1122.2</v>
+        <v>182.2</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>924.7</v>
+        <v>24.7</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>81.5</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4314,31 +4296,31 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>511.7</v>
-      </c>
-      <c r="D46" s="20" t="n">
+        <v>311.7</v>
+      </c>
+      <c r="D46" s="9" t="n">
         <v>29.1</v>
       </c>
-      <c r="E46" s="20" t="n">
+      <c r="E46" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="F46" s="20" t="n">
+      <c r="F46" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="13" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="H46" s="13" t="n">
+      <c r="G46" s="9" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H46" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="I46" s="13" t="n">
-        <v>122.6</v>
+      <c r="I46" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
@@ -4347,7 +4329,7 @@
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>60.5</v>
+        <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>89</v>
@@ -4356,7 +4338,7 @@
         <v>2.4</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>26.2</v>
+        <v>25.2</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>21.6</v>
@@ -4373,10 +4355,10 @@
       <c r="V46" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="13" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X46" s="13" t="n">
+      <c r="W46" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X46" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -140,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -152,13 +164,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -804,37 +822,37 @@
       <c r="K4" s="3" t="n">
         <v>88.8</v>
       </c>
-      <c r="L4" s="8" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="N4" s="3" t="n">
+      <c r="L4" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="N4" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="O4" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="P4" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="R4" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="S4" s="3" t="n">
+      <c r="R4" s="9" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="S4" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="T4" s="3" t="n">
+      <c r="T4" s="9" t="n">
         <v>63.7</v>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="9" t="n">
         <v>15.4</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="9" t="n">
         <v>27.2</v>
       </c>
       <c r="W4" s="3" t="n">
@@ -876,7 +894,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr"/>
       <c r="L5" s="3" t="n">
         <v>19.1</v>
       </c>
@@ -890,10 +908,10 @@
         <v>90</v>
       </c>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="9" t="n">
         <v>19.1</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -905,19 +923,19 @@
       <c r="U5" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="V5" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X5" s="3" t="n">
+      <c r="V5" s="9" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="W5" s="9" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="X5" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="Y5" s="9" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="Z5" s="3" t="n">
+      <c r="Z5" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -960,25 +978,25 @@
       <c r="K6" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="N6" s="3" t="n">
+      <c r="M6" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="N6" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" s="9" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="P6" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="9" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -990,19 +1008,19 @@
       <c r="U6" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V6" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X6" s="3" t="n">
+      <c r="V6" s="9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="W6" s="9" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X6" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="Y6" s="3" t="n">
+      <c r="Y6" s="9" t="n">
         <v>85</v>
       </c>
-      <c r="Z6" s="3" t="n">
+      <c r="Z6" s="9" t="n">
         <v>3.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1033,7 +1051,7 @@
       <c r="G7" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="13" t="n">
         <v>84.8</v>
       </c>
       <c r="I7" s="3" t="n">
@@ -1048,10 +1066,10 @@
       <c r="L7" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" s="16" t="n">
         <v>62</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="13" t="n">
         <v>27.3</v>
       </c>
       <c r="O7" s="3" t="n">
@@ -1060,26 +1078,26 @@
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="S7" s="3" t="n">
+      <c r="Q7" s="9" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="R7" s="9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S7" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="T7" s="3" t="n">
+      <c r="T7" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="U7" s="3" t="n">
+      <c r="U7" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="9" t="n">
         <v>27.6</v>
       </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="8" t="n">
+      <c r="W7" s="12" t="inlineStr"/>
+      <c r="X7" s="13" t="n">
         <v>26.5</v>
       </c>
       <c r="Y7" s="3" t="n">
@@ -1143,10 +1161,10 @@
       <c r="P8" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="9" t="n">
         <v>26</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1158,7 +1176,7 @@
       <c r="U8" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="W8" s="3" t="n">
@@ -1208,13 +1226,13 @@
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="18" t="n">
         <v>44</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="18" t="n">
         <v>94.3</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="18" t="n">
         <v>87.8</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1226,10 +1244,10 @@
       <c r="P9" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="9" t="n">
         <v>138.8</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="18" t="n">
         <v>117.3</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1241,10 +1259,10 @@
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="V9" s="3" t="n">
-        <v>126.1</v>
-      </c>
-      <c r="W9" s="3" t="n">
+      <c r="V9" s="9" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="W9" s="18" t="n">
         <v>113</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1292,25 +1310,25 @@
         <v>6.2</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="18" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="8" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="N10" s="8" t="n">
+      <c r="M10" s="18" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="N10" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="O10" s="3" t="n">
+      <c r="O10" s="9" t="n">
         <v>88.2</v>
       </c>
-      <c r="P10" s="3" t="n">
+      <c r="P10" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="18" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1322,10 +1340,10 @@
       <c r="U10" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="18" t="n">
         <v>25.2</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="18" t="n">
         <v>22.6</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1365,7 +1383,7 @@
       <c r="G11" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="13" t="n">
         <v>85.2</v>
       </c>
       <c r="I11" s="3" t="n">
@@ -1392,7 +1410,7 @@
       <c r="P11" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" s="9" t="n">
         <v>27.9</v>
       </c>
       <c r="R11" s="3" t="n">
@@ -1407,19 +1425,19 @@
       <c r="U11" s="3" t="n">
         <v>58.7</v>
       </c>
-      <c r="V11" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>2471.6</v>
-      </c>
-      <c r="X11" s="3" t="n">
+      <c r="V11" s="9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W11" s="9" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="X11" s="9" t="n">
         <v>31.9</v>
       </c>
-      <c r="Y11" s="3" t="n">
+      <c r="Y11" s="9" t="n">
         <v>97.5</v>
       </c>
-      <c r="Z11" s="3" t="n">
+      <c r="Z11" s="9" t="n">
         <v>0.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1477,34 +1495,34 @@
       <c r="P12" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="R12" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S12" s="3" t="n">
+      <c r="R12" s="9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="S12" s="9" t="n">
         <v>30.8</v>
       </c>
-      <c r="T12" s="3" t="n">
+      <c r="T12" s="9" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="U12" s="3" t="n">
+      <c r="U12" s="9" t="n">
         <v>5.3</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="X12" s="3" t="n">
+      <c r="X12" s="9" t="n">
         <v>30.4</v>
       </c>
-      <c r="Y12" s="3" t="n">
+      <c r="Y12" s="9" t="n">
         <v>97.7</v>
       </c>
-      <c r="Z12" s="3" t="n">
+      <c r="Z12" s="9" t="n">
         <v>0.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -1562,34 +1580,34 @@
       <c r="P13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R13" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="S13" s="3" t="n">
+      <c r="R13" s="9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="S13" s="9" t="n">
         <v>32.7</v>
       </c>
-      <c r="T13" s="3" t="n">
+      <c r="T13" s="9" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="U13" s="3" t="n">
+      <c r="U13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X13" s="3" t="n">
+      <c r="W13" s="9" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="X13" s="9" t="n">
         <v>28.9</v>
       </c>
-      <c r="Y13" s="3" t="n">
+      <c r="Y13" s="9" t="n">
         <v>92.90000000000001</v>
       </c>
-      <c r="Z13" s="3" t="n">
+      <c r="Z13" s="9" t="n">
         <v>2.2</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -1645,34 +1663,34 @@
       <c r="P14" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="R14" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="S14" s="3" t="n">
+      <c r="R14" s="9" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="S14" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="T14" s="3" t="n">
+      <c r="T14" s="9" t="n">
         <v>50.9</v>
       </c>
-      <c r="U14" s="3" t="n">
+      <c r="U14" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="W14" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="X14" s="3" t="n">
+      <c r="W14" s="9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X14" s="9" t="n">
         <v>24.5</v>
       </c>
-      <c r="Y14" s="3" t="n">
+      <c r="Y14" s="9" t="n">
         <v>93</v>
       </c>
-      <c r="Z14" s="3" t="n">
+      <c r="Z14" s="9" t="n">
         <v>1.8</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -1730,7 +1748,7 @@
       <c r="P15" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="9" t="n">
         <v>28.5</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1745,11 +1763,11 @@
       <c r="U15" s="3" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="9" t="n">
         <v>24.5</v>
       </c>
-      <c r="W15" s="3" t="n">
-        <v>21.1</v>
+      <c r="W15" s="9" t="n">
+        <v>19.7</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>22.8</v>
@@ -1797,13 +1815,13 @@
       <c r="J16" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="18" t="n">
         <v>16</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="18" t="n">
         <v>11.2</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="18" t="n">
         <v>924.6</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1815,10 +1833,10 @@
       <c r="P16" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="9" t="n">
         <v>142.8</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="18" t="n">
         <v>23</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1830,11 +1848,11 @@
       <c r="U16" s="3" t="n">
         <v>53.1</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="18" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="3" t="n">
-        <v>115.1</v>
+      <c r="W16" s="9" t="n">
+        <v>113.5</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>137.5</v>
@@ -1883,10 +1901,10 @@
         <v>0.3</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="18" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="18" t="n">
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1898,13 +1916,13 @@
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R17" s="8" t="n">
+      <c r="R17" s="18" t="n">
         <v>8224</v>
       </c>
-      <c r="S17" s="8" t="n">
+      <c r="S17" s="13" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
@@ -1913,19 +1931,19 @@
       <c r="U17" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="W17" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="X17" s="3" t="n">
+      <c r="W17" s="9" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="X17" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="Y17" s="3" t="n">
+      <c r="Y17" s="9" t="n">
         <v>91</v>
       </c>
-      <c r="Z17" s="3" t="n">
+      <c r="Z17" s="9" t="n">
         <v>2.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -1944,7 +1962,7 @@
       <c r="C18" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="16" t="n">
         <v>40.8</v>
       </c>
       <c r="E18" s="3" t="n">
@@ -1968,7 +1986,7 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="9" t="n">
         <v>19.6</v>
       </c>
       <c r="M18" s="3" t="n">
@@ -1986,7 +2004,7 @@
       <c r="Q18" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1998,10 +2016,10 @@
       <c r="U18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="16" t="n">
         <v>50.6</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2053,7 +2071,7 @@
       <c r="K19" s="3" t="n">
         <v>91.5</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="9" t="n">
         <v>19.6</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2068,22 +2086,22 @@
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="S19" s="3" t="n">
+      <c r="Q19" s="9" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="R19" s="9" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="S19" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="T19" s="3" t="n">
+      <c r="T19" s="9" t="n">
         <v>54</v>
       </c>
-      <c r="U19" s="3" t="n">
+      <c r="U19" s="9" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="9" t="n">
         <v>25.8</v>
       </c>
       <c r="W19" s="3" t="n">
@@ -2134,7 +2152,7 @@
       <c r="K20" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="9" t="n">
         <v>20</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2149,10 +2167,10 @@
       <c r="P20" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="16" t="n">
         <v>2.5</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2164,11 +2182,11 @@
       <c r="U20" s="3" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="3" t="n">
-        <v>106.1</v>
+      <c r="W20" s="16" t="n">
+        <v>10.61</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>21.2</v>
@@ -2219,7 +2237,7 @@
       <c r="K21" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2237,7 +2255,7 @@
       <c r="Q21" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2246,10 +2264,10 @@
       <c r="T21" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="U21" s="8" t="n">
+      <c r="U21" s="13" t="n">
         <v>8.9</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="W21" s="3" t="n">
@@ -2283,13 +2301,13 @@
       <c r="D22" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G22" s="13" t="n">
         <v>84.59999999999999</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2304,37 +2322,37 @@
       <c r="K22" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="M22" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="N22" s="3" t="n">
+      <c r="M22" s="9" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="N22" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="O22" s="3" t="n">
+      <c r="O22" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="P22" s="3" t="n">
+      <c r="P22" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="9" t="n">
         <v>30.2</v>
       </c>
-      <c r="R22" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="S22" s="3" t="n">
+      <c r="R22" s="9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S22" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="T22" s="3" t="n">
+      <c r="T22" s="9" t="n">
         <v>56.4</v>
       </c>
-      <c r="U22" s="3" t="n">
+      <c r="U22" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="W22" s="3" t="n">
@@ -2365,13 +2383,13 @@
       <c r="C23" s="3" t="n">
         <v>1925.5</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="18" t="n">
         <v>153.2</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="18" t="n">
         <v>92.8</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="18" t="n">
         <v>123</v>
       </c>
       <c r="G23" s="9" t="n">
@@ -2386,13 +2404,13 @@
       <c r="J23" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="18" t="n">
         <v>495.3</v>
       </c>
-      <c r="L23" s="3" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="M23" s="3" t="n">
+      <c r="L23" s="9" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="M23" s="18" t="n">
         <v>88.2</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2404,11 +2422,11 @@
       <c r="P23" s="3" t="n">
         <v>113.7</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="18" t="n">
         <v>14.6</v>
       </c>
-      <c r="R23" s="3" t="n">
-        <v>1143.1</v>
+      <c r="R23" s="9" t="n">
+        <v>108.7</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>19</v>
@@ -2419,10 +2437,10 @@
       <c r="U23" s="3" t="n">
         <v>85.2</v>
       </c>
-      <c r="V23" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W23" s="3" t="n">
+      <c r="V23" s="9" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="W23" s="18" t="n">
         <v>21</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2450,13 +2468,13 @@
       <c r="C24" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="18" t="n">
         <v>30.6</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="18" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="18" t="n">
         <v>32.6</v>
       </c>
       <c r="G24" s="3" t="n">
@@ -2474,10 +2492,10 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="18" t="n">
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2489,10 +2507,10 @@
       <c r="P24" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="18" t="n">
         <v>2.9</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="18" t="n">
         <v>22.9</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2504,10 +2522,10 @@
       <c r="U24" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="18" t="n">
         <v>22.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2557,35 +2575,35 @@
       <c r="K25" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="N25" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Q25" s="3" t="n">
+      <c r="N25" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="O25" s="9" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="P25" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q25" s="9" t="n">
         <v>31.5</v>
       </c>
-      <c r="R25" s="3" t="n">
+      <c r="R25" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="S25" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>1.8</v>
+      <c r="S25" s="9" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="T25" s="9" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="U25" s="9" t="n">
+        <v>16.4</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>24.2</v>
@@ -2636,40 +2654,40 @@
       <c r="I26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J26" s="8" t="n">
+      <c r="J26" s="13" t="n">
         <v>25.6</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q26" s="3" t="n">
+      <c r="N26" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="P26" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q26" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="R26" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="S26" s="3" t="n">
+      <c r="R26" s="9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S26" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="T26" s="3" t="n">
+      <c r="T26" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="U26" s="3" t="n">
+      <c r="U26" s="9" t="n">
         <v>6</v>
       </c>
       <c r="V26" s="3" t="n">
@@ -2713,7 +2731,7 @@
       <c r="G27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="13" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
@@ -2725,37 +2743,37 @@
       <c r="K27" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="N27" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q27" s="3" t="n">
+      <c r="N27" s="9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="P27" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="S27" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="T27" s="3" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="V27" s="3" t="n">
+      <c r="S27" s="9" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="T27" s="9" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="U27" s="9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="V27" s="16" t="n">
         <v>63.4</v>
       </c>
       <c r="W27" s="3" t="n">
@@ -2810,41 +2828,41 @@
       <c r="K28" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="N28" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="O28" s="3" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q28" s="3" t="n">
+      <c r="N28" s="9" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="O28" s="9" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="P28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="S28" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>1.3</v>
+      <c r="S28" s="9" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="T28" s="9" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="U28" s="9" t="n">
+        <v>10.2</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="W28" s="3" t="n">
-        <v>956.1</v>
+      <c r="W28" s="16" t="n">
+        <v>95.61</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>27.6</v>
@@ -2895,49 +2913,49 @@
       <c r="K29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q29" s="3" t="n">
+      <c r="N29" s="9" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="O29" s="9" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="P29" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q29" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="S29" s="8" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="T29" s="3" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="V29" s="3" t="n">
+      <c r="S29" s="9" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="T29" s="9" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="U29" s="9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="V29" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="W29" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="X29" s="3" t="n">
+      <c r="W29" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="X29" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="Y29" s="3" t="n">
+      <c r="Y29" s="9" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="Z29" s="3" t="n">
+      <c r="Z29" s="9" t="n">
         <v>6.1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -2977,13 +2995,13 @@
       <c r="J30" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="18" t="n">
         <v>25.4</v>
       </c>
-      <c r="L30" s="3" t="n">
-        <v>929.6</v>
-      </c>
-      <c r="M30" s="3" t="n">
+      <c r="L30" s="9" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="M30" s="9" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -2995,11 +3013,11 @@
       <c r="P30" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q30" s="3" t="n">
-        <v>238.5</v>
-      </c>
-      <c r="R30" s="3" t="n">
-        <v>113.7</v>
+      <c r="Q30" s="9" t="n">
+        <v>138.7</v>
+      </c>
+      <c r="R30" s="9" t="n">
+        <v>112.2</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>122.7</v>
@@ -3010,10 +3028,10 @@
       <c r="U30" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="18" t="n">
         <v>123.1</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="18" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3053,7 +3071,7 @@
       <c r="G31" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="13" t="n">
         <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
@@ -3063,40 +3081,40 @@
         <v>3.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="N31" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q31" s="3" t="n">
+      <c r="N31" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="O31" s="9" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="P31" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q31" s="9" t="n">
         <v>27.7</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="18" t="n">
         <v>22.7</v>
       </c>
-      <c r="S31" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V31" s="8" t="n">
+      <c r="S31" s="9" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T31" s="9" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="U31" s="9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="V31" s="18" t="n">
         <v>824.6</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="18" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3146,22 +3164,22 @@
       <c r="K32" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M32" s="3" t="n">
+      <c r="M32" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="N32" s="8" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q32" s="3" t="n">
+      <c r="N32" s="9" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="O32" s="9" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="P32" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q32" s="9" t="n">
         <v>31</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3179,7 +3197,7 @@
       <c r="V32" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="13" t="n">
         <v>23.4</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3231,34 +3249,34 @@
       <c r="K33" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="M33" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="N33" s="3" t="n">
+      <c r="M33" s="9" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N33" s="9" t="n">
         <v>21.7</v>
       </c>
-      <c r="O33" s="3" t="n">
+      <c r="O33" s="9" t="n">
         <v>87.40000000000001</v>
       </c>
-      <c r="P33" s="3" t="n">
+      <c r="P33" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="9" t="n">
         <v>32.9</v>
       </c>
-      <c r="R33" s="8" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="S33" s="3" t="n">
+      <c r="R33" s="9" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="S33" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="T33" s="3" t="n">
+      <c r="T33" s="9" t="n">
         <v>47.7</v>
       </c>
-      <c r="U33" s="3" t="n">
+      <c r="U33" s="9" t="n">
         <v>26.1</v>
       </c>
       <c r="V33" s="3" t="n">
@@ -3316,37 +3334,37 @@
       <c r="K34" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="N34" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="O34" s="3" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q34" s="3" t="n">
+      <c r="N34" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="O34" s="9" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="P34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="9" t="n">
         <v>26.1</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S34" s="3" t="n">
+      <c r="R34" s="9" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="S34" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="T34" s="3" t="n">
+      <c r="T34" s="9" t="n">
         <v>78.59999999999999</v>
       </c>
-      <c r="U34" s="3" t="n">
+      <c r="U34" s="9" t="n">
         <v>7.2</v>
       </c>
-      <c r="V34" s="8" t="n">
+      <c r="V34" s="13" t="n">
         <v>25.5</v>
       </c>
       <c r="W34" s="3" t="n">
@@ -3401,22 +3419,22 @@
       <c r="K35" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="N35" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q35" s="3" t="n">
+      <c r="N35" s="9" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="O35" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="P35" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q35" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="R35" s="3" t="n">
@@ -3486,37 +3504,37 @@
       <c r="K36" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="9" t="n">
         <v>19.4</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q36" s="3" t="n">
+      <c r="N36" s="9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="P36" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q36" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="R36" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="S36" s="3" t="n">
+      <c r="R36" s="9" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S36" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="T36" s="3" t="n">
+      <c r="T36" s="9" t="n">
         <v>72.3</v>
       </c>
-      <c r="U36" s="3" t="n">
+      <c r="U36" s="9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="8" t="n">
+      <c r="V36" s="16" t="n">
         <v>58</v>
       </c>
       <c r="W36" s="3" t="n">
@@ -3566,28 +3584,28 @@
       <c r="J37" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="18" t="n">
         <v>10.2</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="9" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="18" t="n">
         <v>96.5</v>
       </c>
-      <c r="N37" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v>437.5</v>
-      </c>
-      <c r="P37" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="Q37" s="3" t="n">
+      <c r="N37" s="9" t="n">
+        <v>921</v>
+      </c>
+      <c r="O37" s="9" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="P37" s="9" t="n">
+        <v>267.8</v>
+      </c>
+      <c r="Q37" s="9" t="n">
         <v>139.6</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="18" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3599,10 +3617,10 @@
       <c r="U37" s="3" t="n">
         <v>65.7</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="18" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="18" t="n">
         <v>112.2</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3630,13 +3648,13 @@
       <c r="C38" s="3" t="n">
         <v>336.7</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="18" t="n">
         <v>30</v>
       </c>
       <c r="E38" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="F38" s="18" t="n">
         <v>25.1</v>
       </c>
       <c r="G38" s="9" t="n">
@@ -3654,25 +3672,25 @@
       <c r="K38" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="N38" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="P38" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="3" t="n">
+      <c r="N38" s="9" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="O38" s="9" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="P38" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q38" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="18" t="n">
         <v>23.1</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3684,10 +3702,10 @@
       <c r="U38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="18" t="n">
         <v>25.2</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="18" t="n">
         <v>224.1</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3724,10 +3742,10 @@
       <c r="F39" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G39" s="13" t="n">
         <v>58.5</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="13" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="I39" s="3" t="inlineStr"/>
@@ -3737,13 +3755,13 @@
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="L39" s="9" t="n">
         <v>20.5</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="8" t="n">
+      <c r="N39" s="13" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="O39" s="3" t="n">
@@ -3752,10 +3770,10 @@
       <c r="P39" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="16" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3810,7 +3828,7 @@
       <c r="G40" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="H40" s="13" t="n">
         <v>89</v>
       </c>
       <c r="I40" s="3" t="n">
@@ -3822,7 +3840,7 @@
       <c r="K40" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="9" t="n">
         <v>20.4</v>
       </c>
       <c r="M40" s="3" t="n">
@@ -3837,22 +3855,22 @@
       <c r="P40" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="R40" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S40" s="3" t="n">
+      <c r="R40" s="9" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="S40" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="T40" s="3" t="n">
+      <c r="T40" s="9" t="n">
         <v>89.7</v>
       </c>
-      <c r="U40" s="3" t="n">
+      <c r="U40" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="8" t="n">
+      <c r="V40" s="13" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="W40" s="3" t="n">
@@ -3907,7 +3925,7 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="M41" s="3" t="n">
@@ -3925,7 +3943,7 @@
       <c r="Q41" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3943,7 +3961,7 @@
       <c r="W41" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="X41" s="8" t="n">
+      <c r="X41" s="13" t="n">
         <v>25.2</v>
       </c>
       <c r="Y41" s="3" t="n">
@@ -3992,7 +4010,7 @@
       <c r="K42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="9" t="n">
         <v>17.2</v>
       </c>
       <c r="M42" s="3" t="n">
@@ -4010,10 +4028,10 @@
       <c r="Q42" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S42" s="8" t="n">
+      <c r="S42" s="13" t="n">
         <v>28.2</v>
       </c>
       <c r="T42" s="3" t="n">
@@ -4077,7 +4095,7 @@
       <c r="K43" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="9" t="n">
         <v>19</v>
       </c>
       <c r="M43" s="3" t="n">
@@ -4095,7 +4113,7 @@
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="9" t="n">
         <v>22.3</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4162,10 +4180,10 @@
       <c r="K44" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" s="9" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="8" t="n">
+      <c r="M44" s="13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="N44" s="3" t="n">
@@ -4180,7 +4198,7 @@
       <c r="Q44" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" s="9" t="n">
         <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4195,7 +4213,7 @@
       <c r="V44" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="W44" s="12" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4236,13 +4254,13 @@
       <c r="J45" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="L45" s="3" t="n">
-        <v>1910.4</v>
-      </c>
-      <c r="M45" s="3" t="inlineStr"/>
+      <c r="L45" s="9" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="M45" s="14" t="inlineStr"/>
       <c r="N45" s="3" t="n">
         <v>10092105.9</v>
       </c>
@@ -4252,11 +4270,11 @@
       <c r="P45" s="3" t="n">
         <v>140.4</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="18" t="n">
         <v>257.5</v>
       </c>
-      <c r="R45" s="3" t="n">
-        <v>129.2</v>
+      <c r="R45" s="9" t="n">
+        <v>129.1</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>1382</v>
@@ -4267,10 +4285,10 @@
       <c r="U45" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="18" t="n">
         <v>12.2</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="18" t="n">
         <v>182.2</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4310,7 +4328,7 @@
       <c r="G46" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="13" t="n">
         <v>17.6</v>
       </c>
       <c r="I46" s="3" t="n">
@@ -4322,7 +4340,7 @@
       <c r="K46" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="9" t="n">
         <v>19.4</v>
       </c>
       <c r="M46" s="3" t="n">
@@ -4337,10 +4355,10 @@
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="18" t="n">
         <v>25.2</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4352,10 +4370,10 @@
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="18" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="18" t="n">
         <v>21.8</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
       </patternFill>
@@ -49,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,37 +152,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -796,22 +808,22 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="D4" s="9" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="D4" s="10" t="n">
         <v>31.2</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="10" t="n">
         <v>14</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>91124.10000000001</v>
+        <v>27.4</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.1</v>
@@ -820,47 +832,53 @@
         <v>4.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="L4" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L4" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="10" t="n">
         <v>15.4</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="N4" s="10" t="n">
         <v>17.5</v>
       </c>
-      <c r="O4" s="9" t="n">
+      <c r="O4" s="10" t="n">
         <v>87</v>
       </c>
-      <c r="P4" s="9" t="n">
+      <c r="P4" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="10" t="n">
         <v>22.4</v>
       </c>
-      <c r="S4" s="9" t="n">
+      <c r="S4" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="T4" s="10" t="n">
         <v>63.7</v>
       </c>
-      <c r="U4" s="9" t="n">
+      <c r="U4" s="10" t="n">
         <v>15.4</v>
       </c>
-      <c r="V4" s="9" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="W4" s="3" t="n">
+      <c r="V4" s="10" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="W4" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="X4" s="3" t="inlineStr"/>
-      <c r="Y4" s="3" t="inlineStr"/>
-      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="X4" s="10" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="Y4" s="10" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="Z4" s="10" t="n">
+        <v>7.3</v>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -875,67 +893,73 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F5" s="9" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F5" s="10" t="n">
         <v>21.5</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="10" t="n">
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="12" t="inlineStr"/>
-      <c r="L5" s="3" t="n">
+      <c r="K5" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="L5" s="10" t="n">
         <v>19.1</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="N5" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="9" t="n">
+      <c r="N5" s="10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="P5" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q5" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="R5" s="9" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="S5" s="3" t="n">
+      <c r="R5" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="S5" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="T5" s="3" t="n">
+      <c r="T5" s="10" t="n">
         <v>87.8</v>
       </c>
-      <c r="U5" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V5" s="9" t="n">
+      <c r="U5" s="10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V5" s="10" t="n">
         <v>27.7</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="10" t="n">
         <v>22.7</v>
       </c>
-      <c r="X5" s="9" t="n">
+      <c r="X5" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="Y5" s="9" t="n">
+      <c r="Y5" s="10" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="Z5" s="9" t="n">
+      <c r="Z5" s="10" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -952,75 +976,75 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>432.6</v>
-      </c>
-      <c r="D6" s="9" t="n">
+        <v>421.6</v>
+      </c>
+      <c r="D6" s="10" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <v>25.6</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="10" t="n">
         <v>11.6</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>18.5</v>
+        <v>2.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="K6" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K6" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="10" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="N6" s="9" t="n">
+      <c r="N6" s="10" t="n">
         <v>21.1</v>
       </c>
-      <c r="O6" s="9" t="n">
+      <c r="O6" s="10" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="P6" s="9" t="n">
+      <c r="P6" s="10" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="10" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="S6" s="3" t="n">
+      <c r="R6" s="10" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="S6" s="10" t="n">
         <v>25.9</v>
       </c>
-      <c r="T6" s="3" t="n">
+      <c r="T6" s="10" t="n">
         <v>61.9</v>
       </c>
-      <c r="U6" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="V6" s="9" t="n">
+      <c r="U6" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="V6" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="10" t="n">
         <v>18.1</v>
       </c>
-      <c r="X6" s="9" t="n">
+      <c r="X6" s="10" t="n">
         <v>20.7</v>
       </c>
-      <c r="Y6" s="9" t="n">
+      <c r="Y6" s="10" t="n">
         <v>85</v>
       </c>
-      <c r="Z6" s="9" t="n">
+      <c r="Z6" s="10" t="n">
         <v>3.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1039,72 +1063,74 @@
       <c r="C7" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="13" t="n">
-        <v>84.8</v>
+      <c r="H7" s="18" t="n">
+        <v>14.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M7" s="16" t="n">
-        <v>62</v>
-      </c>
-      <c r="N7" s="13" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q7" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="N7" s="10" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="P7" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q7" s="10" t="n">
         <v>31.9</v>
       </c>
-      <c r="R7" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S7" s="9" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="T7" s="9" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="U7" s="9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="V7" s="9" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="W7" s="12" t="inlineStr"/>
-      <c r="X7" s="13" t="n">
+      <c r="R7" s="10" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="S7" s="10" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="T7" s="10" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="U7" s="10" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="V7" s="10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="W7" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="X7" s="10" t="n">
         <v>26.5</v>
       </c>
-      <c r="Y7" s="3" t="n">
-        <v>727.9</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>17.5</v>
+      <c r="Y7" s="10" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="Z7" s="10" t="n">
+        <v>7.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1120,18 +1146,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>297.6</v>
-      </c>
-      <c r="D8" s="9" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="D8" s="10" t="n">
         <v>32.6</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="10" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1146,49 +1172,51 @@
       <c r="K8" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q8" s="9" t="n">
+      <c r="M8" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="P8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="S8" s="3" t="n">
+      <c r="R8" s="10" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="S8" s="10" t="n">
         <v>33.2</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="T8" s="10" t="n">
         <v>95.40000000000001</v>
       </c>
-      <c r="U8" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="V8" s="9" t="n">
+      <c r="U8" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V8" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="10" t="n">
         <v>22.8</v>
       </c>
-      <c r="X8" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="X8" s="10" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="Y8" s="10" t="n">
+        <v>93</v>
+      </c>
+      <c r="Z8" s="10" t="n">
+        <v>2.1</v>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1205,53 +1233,53 @@
       <c r="C9" s="3" t="n">
         <v>166.6</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>152.6</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="F9" s="9" t="n">
+      <c r="D9" s="10" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="F9" s="10" t="n">
         <v>122.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>80.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>22.2</v>
+        <v>11.2</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K9" s="18" t="n">
-        <v>44</v>
-      </c>
-      <c r="L9" s="18" t="n">
+      <c r="K9" s="22" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="L9" s="10" t="n">
         <v>94.3</v>
       </c>
-      <c r="M9" s="18" t="n">
+      <c r="M9" s="22" t="n">
         <v>87.8</v>
       </c>
-      <c r="N9" s="3" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>440.9</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="Q9" s="9" t="n">
+      <c r="N9" s="10" t="n">
+        <v>660.6</v>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="P9" s="10" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="Q9" s="10" t="n">
         <v>138.8</v>
       </c>
-      <c r="R9" s="18" t="n">
-        <v>117.3</v>
+      <c r="R9" s="10" t="n">
+        <v>112.2</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1231.9</v>
+        <v>131.9</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>360.9</v>
@@ -1259,20 +1287,20 @@
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="V9" s="9" t="n">
-        <v>127.1</v>
-      </c>
-      <c r="W9" s="18" t="n">
+      <c r="V9" s="10" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="W9" s="22" t="n">
         <v>113</v>
       </c>
-      <c r="X9" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>114102.4</v>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <v>38.8</v>
+      <c r="X9" s="10" t="n">
+        <v>1654.3</v>
+      </c>
+      <c r="Y9" s="10" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="Z9" s="10" t="n">
+        <v>883.1</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1290,70 +1318,74 @@
       <c r="C10" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="10" t="n">
         <v>30.5</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="10" t="n">
         <v>18.5</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="10" t="n">
         <v>24.5</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="10" t="n">
         <v>12</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
+        <v>16.1</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J10" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L10" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="18" t="n">
+      <c r="M10" s="22" t="n">
         <v>16.9</v>
       </c>
-      <c r="N10" s="9" t="n">
+      <c r="N10" s="10" t="n">
         <v>19.3</v>
       </c>
-      <c r="O10" s="9" t="n">
+      <c r="O10" s="10" t="n">
         <v>88.2</v>
       </c>
-      <c r="P10" s="9" t="n">
+      <c r="P10" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" s="10" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="18" t="n">
+      <c r="R10" s="22" t="n">
         <v>23.5</v>
       </c>
-      <c r="S10" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="V10" s="18" t="n">
+      <c r="S10" s="10" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="T10" s="10" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="U10" s="10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="V10" s="10" t="n">
         <v>25.2</v>
       </c>
-      <c r="W10" s="18" t="n">
+      <c r="W10" s="22" t="n">
         <v>22.6</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>6.6</v>
+      <c r="X10" s="10" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="Y10" s="10" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="Z10" s="10" t="n">
+        <v>4.6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1369,76 +1401,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2445.1</v>
-      </c>
-      <c r="D11" s="9" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="D11" s="10" t="n">
         <v>28.7</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="10" t="n">
         <v>24.3</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>85.2</v>
+      <c r="G11" s="10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="O11" s="10" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="P11" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q11" s="10" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="R11" s="10" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="S11" s="10" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="T11" s="10" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="U11" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V11" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="W11" s="10" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X11" s="10" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="Y11" s="10" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="Z11" s="10" t="n">
         <v>0.6</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q11" s="9" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="V11" s="9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="W11" s="9" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="X11" s="9" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="Y11" s="9" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="Z11" s="9" t="n">
-        <v>0.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1454,22 +1486,22 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>383.3</v>
-      </c>
-      <c r="D12" s="9" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="D12" s="10" t="n">
         <v>28.1</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="10" t="n">
         <v>23.9</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="10" t="n">
         <v>8.5</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.9</v>
@@ -1478,9 +1510,9 @@
         <v>3.2</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="M12" s="3" t="n">
@@ -1493,37 +1525,37 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q12" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="Q12" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="R12" s="9" t="n">
+      <c r="R12" s="10" t="n">
         <v>24.5</v>
       </c>
-      <c r="S12" s="9" t="n">
+      <c r="S12" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="T12" s="9" t="n">
+      <c r="T12" s="10" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="U12" s="9" t="n">
+      <c r="U12" s="10" t="n">
         <v>5.3</v>
       </c>
-      <c r="V12" s="9" t="n">
+      <c r="V12" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="W12" s="9" t="n">
+      <c r="W12" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="X12" s="9" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="Y12" s="9" t="n">
-        <v>97.7</v>
-      </c>
-      <c r="Z12" s="9" t="n">
-        <v>0.7</v>
+      <c r="X12" s="10" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="Y12" s="10" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="Z12" s="10" t="n">
+        <v>0.6</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1539,18 +1571,18 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="D13" s="9" t="n">
+        <v>235.6</v>
+      </c>
+      <c r="D13" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="10" t="n">
         <v>25.5</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="10" t="n">
         <v>11.3</v>
       </c>
       <c r="H13" s="3" t="n">
@@ -1565,7 +1597,7 @@
       <c r="K13" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="10" t="n">
         <v>20</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1580,35 +1612,35 @@
       <c r="P13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="10" t="n">
         <v>25.5</v>
       </c>
-      <c r="S13" s="9" t="n">
+      <c r="S13" s="10" t="n">
         <v>32.7</v>
       </c>
-      <c r="T13" s="9" t="n">
+      <c r="T13" s="10" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="U13" s="9" t="n">
+      <c r="U13" s="10" t="n">
         <v>6.4</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="9" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="X13" s="9" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="Y13" s="9" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="Z13" s="9" t="n">
-        <v>2.2</v>
+      <c r="W13" s="10" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X13" s="10" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="Y13" s="10" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="Z13" s="10" t="n">
+        <v>1.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1624,74 +1656,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="D14" s="9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="D14" s="10" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="10" t="n">
         <v>26.1</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="10" t="n">
         <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="n">
+        <v>3.3</v>
+      </c>
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="N14" s="3" t="n">
+      <c r="M14" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="N14" s="10" t="n">
         <v>20.8</v>
       </c>
-      <c r="O14" s="3" t="n">
+      <c r="O14" s="10" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="P14" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q14" s="9" t="n">
+      <c r="P14" s="10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q14" s="10" t="n">
         <v>30.6</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" s="10" t="n">
         <v>19.2</v>
       </c>
-      <c r="S14" s="9" t="n">
+      <c r="S14" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="T14" s="9" t="n">
+      <c r="T14" s="10" t="n">
         <v>50.9</v>
       </c>
-      <c r="U14" s="9" t="n">
+      <c r="U14" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="W14" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X14" s="9" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="Y14" s="9" t="n">
-        <v>93</v>
-      </c>
-      <c r="Z14" s="9" t="n">
-        <v>1.8</v>
+      <c r="W14" s="10" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="X14" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y14" s="10" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="Z14" s="10" t="n">
+        <v>1.3</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1707,22 +1741,22 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="D15" s="9" t="n">
+        <v>143.3</v>
+      </c>
+      <c r="D15" s="10" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F15" s="9" t="n">
+      <c r="E15" s="10" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F15" s="10" t="n">
         <v>24.9</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="10" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>89.8</v>
+        <v>19.8</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>1.9</v>
@@ -1731,13 +1765,13 @@
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="L15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="M15" s="3" t="n">
-        <v>19.1</v>
+      <c r="M15" s="18" t="n">
+        <v>29.1</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>21.3</v>
@@ -1748,35 +1782,35 @@
       <c r="P15" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="10" t="n">
         <v>28.5</v>
       </c>
-      <c r="R15" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="S15" s="3" t="n">
+      <c r="R15" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="S15" s="10" t="n">
         <v>24.8</v>
       </c>
-      <c r="T15" s="3" t="n">
+      <c r="T15" s="10" t="n">
         <v>63.8</v>
       </c>
-      <c r="U15" s="3" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="V15" s="9" t="n">
+      <c r="U15" s="10" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="V15" s="10" t="n">
         <v>24.5</v>
       </c>
-      <c r="W15" s="9" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="Y15" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v>17.9</v>
+      <c r="W15" s="10" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="X15" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y15" s="10" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="Z15" s="10" t="n">
+        <v>5.7</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1792,76 +1826,74 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>199.2</v>
-      </c>
-      <c r="D16" s="9" t="n">
+        <v>1992.8</v>
+      </c>
+      <c r="D16" s="10" t="n">
         <v>149.9</v>
       </c>
-      <c r="E16" s="9" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="F16" s="9" t="n">
+      <c r="E16" s="22" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F16" s="10" t="n">
         <v>124.7</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="19" t="n">
         <v>50.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>8.1</v>
+        <v>11.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>16</v>
-      </c>
-      <c r="L16" s="18" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M16" s="18" t="n">
-        <v>924.6</v>
+        <v>115.8</v>
+      </c>
+      <c r="K16" s="16" t="inlineStr"/>
+      <c r="L16" s="10" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="M16" s="22" t="n">
+        <v>194.6</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>105.8</v>
+        <v>105.2</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>444.8</v>
+        <v>444.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="10" t="n">
         <v>142.8</v>
       </c>
-      <c r="R16" s="18" t="n">
-        <v>23</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>142.5</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>368.7</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="V16" s="18" t="n">
+      <c r="R16" s="22" t="n">
+        <v>123</v>
+      </c>
+      <c r="S16" s="10" t="n">
+        <v>2299.5</v>
+      </c>
+      <c r="T16" s="10" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="U16" s="10" t="n">
+        <v>1897.7</v>
+      </c>
+      <c r="V16" s="10" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="9" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>137.5</v>
-      </c>
-      <c r="Y16" s="3" t="n">
-        <v>455.1</v>
-      </c>
-      <c r="Z16" s="3" t="n">
-        <v>13.4</v>
+      <c r="W16" s="10" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="X16" s="10" t="n">
+        <v>1775.4</v>
+      </c>
+      <c r="Y16" s="10" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="Z16" s="10" t="n">
+        <v>366.6</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1877,73 +1909,75 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="D17" s="9" t="n">
+        <v>399.8</v>
+      </c>
+      <c r="D17" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <v>24.9</v>
       </c>
-      <c r="G17" s="9" t="n">
-        <v>10</v>
+      <c r="G17" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>18.1</v>
+        <v>28.1</v>
       </c>
       <c r="I17" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>11551.5</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="M17" s="22" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="O17" s="10" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="P17" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q17" s="10" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="R17" s="22" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="S17" s="10" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="T17" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="U17" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="M17" s="18" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q17" s="9" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="R17" s="18" t="n">
-        <v>8224</v>
-      </c>
-      <c r="S17" s="13" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="22" t="n">
         <v>22.7</v>
       </c>
-      <c r="X17" s="9" t="n">
+      <c r="X17" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="Y17" s="9" t="n">
+      <c r="Y17" s="10" t="n">
         <v>91</v>
       </c>
-      <c r="Z17" s="9" t="n">
+      <c r="Z17" s="10" t="n">
         <v>2.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -1960,75 +1994,75 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="E18" s="3" t="n">
+        <v>431.1</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E18" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>14.9</v>
+      <c r="F18" s="10" t="n">
+        <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.1</v>
+        <v>14.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>24.9</v>
+        <v>13.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="9" t="n">
-        <v>19.6</v>
+      <c r="L18" s="10" t="n">
+        <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>27.7</v>
+        <v>20.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.9</v>
+        <v>13.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q18" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q18" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="R18" s="9" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="S18" s="3" t="n">
+      <c r="R18" s="10" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="S18" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="T18" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U18" s="3" t="n">
+      <c r="T18" s="10" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="U18" s="10" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="16" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="X18" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="Y18" s="3" t="n">
+      <c r="W18" s="10" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="X18" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="Y18" s="10" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="Z18" s="3" t="n">
+      <c r="Z18" s="10" t="n">
         <v>2.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2045,16 +2079,16 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>433.6</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>25.4</v>
+        <v>2223.4</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>25.5</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>18.4</v>
@@ -2066,16 +2100,16 @@
         <v>2.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="L19" s="9" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="L19" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>28.2</v>
+      <c r="M19" s="18" t="n">
+        <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>20</v>
@@ -2086,34 +2120,36 @@
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="Q19" s="10" t="n">
         <v>31.8</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="S19" s="9" t="n">
+      <c r="S19" s="10" t="n">
         <v>25.3</v>
       </c>
-      <c r="T19" s="9" t="n">
+      <c r="T19" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="U19" s="9" t="n">
+      <c r="U19" s="10" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="10" t="n">
         <v>25.8</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="10" t="n">
         <v>23.3</v>
       </c>
-      <c r="X19" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y19" s="3" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="Z19" s="3" t="inlineStr"/>
+      <c r="X19" s="10" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y19" s="10" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="Z19" s="10" t="n">
+        <v>4.6</v>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2128,19 +2164,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>956.8</v>
-      </c>
-      <c r="D20" s="9" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D20" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="10" t="n">
         <v>23.5</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>17.4</v>
+      <c r="G20" s="10" t="n">
+        <v>7.4</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>1.8</v>
@@ -2148,11 +2184,13 @@
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K20" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="L20" s="9" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="L20" s="10" t="n">
         <v>20</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2162,40 +2200,40 @@
         <v>20.9</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>289</v>
+        <v>89</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q20" s="16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R20" s="9" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="S20" s="3" t="n">
+      <c r="Q20" s="10" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="R20" s="10" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S20" s="10" t="n">
         <v>23.1</v>
       </c>
-      <c r="T20" s="3" t="n">
-        <v>707.2</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="V20" s="9" t="n">
+      <c r="T20" s="10" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="U20" s="10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V20" s="10" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="16" t="n">
-        <v>10.61</v>
-      </c>
-      <c r="X20" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Y20" s="3" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="Z20" s="3" t="n">
-        <v>10.2</v>
+      <c r="W20" s="10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="X20" s="10" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="Y20" s="10" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="Z20" s="10" t="n">
+        <v>7.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2213,16 +2251,16 @@
       <c r="C21" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="10" t="n">
         <v>24.6</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="10" t="n">
         <v>12.4</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2237,50 +2275,50 @@
       <c r="K21" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="M21" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="N21" s="3" t="n">
+      <c r="M21" s="10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N21" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="O21" s="3" t="n">
+      <c r="O21" s="10" t="n">
         <v>86.7</v>
       </c>
-      <c r="P21" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q21" s="3" t="n">
+      <c r="P21" s="10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q21" s="10" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="U21" s="13" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="V21" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="V21" s="10" t="n">
         <v>24.3</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="10" t="n">
         <v>22.4</v>
       </c>
-      <c r="X21" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="Y21" s="3" t="n">
-        <v>850.8</v>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v>14.5</v>
+      <c r="X21" s="10" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="Y21" s="10" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="Z21" s="10" t="n">
+        <v>3.3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2296,19 +2334,19 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>374.1</v>
-      </c>
-      <c r="D22" s="3" t="n">
+        <v>2374.6</v>
+      </c>
+      <c r="D22" s="10" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="G22" s="13" t="n">
-        <v>84.59999999999999</v>
+      <c r="E22" s="10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>1.5</v>
@@ -2322,50 +2360,50 @@
       <c r="K22" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" s="10" t="n">
         <v>15.4</v>
       </c>
-      <c r="N22" s="9" t="n">
+      <c r="N22" s="10" t="n">
         <v>17.5</v>
       </c>
-      <c r="O22" s="9" t="n">
+      <c r="O22" s="10" t="n">
         <v>87</v>
       </c>
-      <c r="P22" s="9" t="n">
+      <c r="P22" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q22" s="9" t="n">
+      <c r="Q22" s="10" t="n">
         <v>30.2</v>
       </c>
-      <c r="R22" s="9" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="S22" s="9" t="n">
+      <c r="R22" s="3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="S22" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="T22" s="9" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="U22" s="9" t="n">
+      <c r="T22" s="3" t="n">
+        <v>256.4</v>
+      </c>
+      <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="9" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="W22" s="3" t="n">
+      <c r="V22" s="10" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="W22" s="10" t="n">
         <v>19.5</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="Y22" s="3" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>3.6</v>
+      <c r="X22" s="10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="Y22" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z22" s="10" t="n">
+        <v>2.5</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2381,19 +2419,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1925.5</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>153.2</v>
-      </c>
-      <c r="E23" s="18" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="E23" s="10" t="n">
         <v>92.8</v>
       </c>
-      <c r="F23" s="18" t="n">
+      <c r="F23" s="22" t="n">
         <v>123</v>
       </c>
-      <c r="G23" s="9" t="n">
-        <v>60.6</v>
+      <c r="G23" s="10" t="n">
+        <v>60.5</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>85.59999999999999</v>
@@ -2402,15 +2440,15 @@
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="K23" s="18" t="n">
-        <v>495.3</v>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="M23" s="18" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="K23" s="22" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="M23" s="22" t="n">
         <v>88.2</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2422,35 +2460,35 @@
       <c r="P23" s="3" t="n">
         <v>113.7</v>
       </c>
-      <c r="Q23" s="18" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="R23" s="9" t="n">
-        <v>108.7</v>
+      <c r="Q23" s="10" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="R23" s="22" t="n">
+        <v>114.3</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>295.2</v>
+        <v>2895.2</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="V23" s="9" t="n">
-        <v>122.5</v>
-      </c>
-      <c r="W23" s="18" t="n">
-        <v>21</v>
+        <v>85.40000000000001</v>
+      </c>
+      <c r="V23" s="10" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="W23" s="10" t="n">
+        <v>110.3</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>226.7</v>
+        <v>126.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1411</v>
+        <v>411</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>27.1</v>
+        <v>0.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2466,22 +2504,22 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="D24" s="18" t="n">
+        <v>1398.5</v>
+      </c>
+      <c r="D24" s="10" t="n">
         <v>30.6</v>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E24" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="18" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>1.7</v>
+      <c r="F24" s="10" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2492,14 +2530,14 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="9" t="n">
+      <c r="L24" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="18" t="n">
+      <c r="M24" s="22" t="n">
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>19.3</v>
+        <v>12.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>87.40000000000001</v>
@@ -2507,10 +2545,10 @@
       <c r="P24" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q24" s="18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R24" s="18" t="n">
+      <c r="Q24" s="10" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="R24" s="22" t="n">
         <v>22.9</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2520,20 +2558,22 @@
         <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V24" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="V24" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="W24" s="18" t="n">
+      <c r="W24" s="10" t="n">
         <v>22.1</v>
       </c>
-      <c r="X24" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="Y24" s="3" t="inlineStr"/>
-      <c r="Z24" s="3" t="n">
-        <v>5.4</v>
+      <c r="X24" s="10" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="Y24" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="Z24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2549,25 +2589,25 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="D25" s="9" t="n">
+        <v>2374</v>
+      </c>
+      <c r="D25" s="10" t="n">
         <v>32.1</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="10" t="n">
         <v>19.3</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="10" t="n">
         <v>25.7</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="10" t="n">
         <v>12.8</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>3.6</v>
@@ -2575,50 +2615,50 @@
       <c r="K25" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L25" s="9" t="n">
+      <c r="L25" s="10" t="n">
         <v>19.5</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="N25" s="9" t="n">
+      <c r="N25" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="O25" s="9" t="n">
+      <c r="O25" s="10" t="n">
         <v>93.40000000000001</v>
       </c>
-      <c r="P25" s="9" t="n">
+      <c r="P25" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q25" s="9" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="R25" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="S25" s="9" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="T25" s="9" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="U25" s="9" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="V25" s="3" t="n">
+      <c r="Q25" s="10" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="R25" s="10" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="S25" s="10" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="T25" s="10" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="U25" s="10" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="V25" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="10" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>174.8</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>7.5</v>
+      <c r="X25" s="10" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="Y25" s="10" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="Z25" s="10" t="n">
+        <v>5.5</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2634,74 +2674,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>329.2</v>
-      </c>
-      <c r="D26" s="9" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="D26" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="10" t="n">
         <v>12.2</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J26" s="13" t="n">
-        <v>25.6</v>
+      <c r="J26" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="N26" s="9" t="n">
+      <c r="N26" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="O26" s="9" t="n">
+      <c r="O26" s="10" t="n">
         <v>91.59999999999999</v>
       </c>
-      <c r="P26" s="9" t="n">
+      <c r="P26" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="R26" s="9" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="S26" s="9" t="n">
+      <c r="R26" s="10" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S26" s="10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="T26" s="10" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="U26" s="10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V26" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="T26" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="U26" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="W26" s="3" t="n">
+      <c r="W26" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="X26" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="Y26" s="3" t="inlineStr"/>
-      <c r="Z26" s="3" t="n">
-        <v>17.6</v>
+      <c r="X26" s="10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="Y26" s="10" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="Z26" s="10" t="n">
+        <v>4.1</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2717,25 +2759,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>354.8</v>
-      </c>
-      <c r="D27" s="9" t="n">
+        <v>1354.4</v>
+      </c>
+      <c r="D27" s="10" t="n">
         <v>28.2</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="H27" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>2.9</v>
@@ -2743,50 +2785,50 @@
       <c r="K27" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="N27" s="9" t="n">
+      <c r="N27" s="10" t="n">
         <v>21.7</v>
       </c>
-      <c r="O27" s="9" t="n">
+      <c r="O27" s="10" t="n">
         <v>91.7</v>
       </c>
-      <c r="P27" s="9" t="n">
+      <c r="P27" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="R27" s="9" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S27" s="9" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="T27" s="9" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="U27" s="9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="V27" s="16" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="W27" s="3" t="n">
+      <c r="R27" s="10" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="S27" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="T27" s="10" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="U27" s="10" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V27" s="10" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="W27" s="10" t="n">
         <v>20.8</v>
       </c>
-      <c r="X27" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>5.4</v>
+      <c r="X27" s="10" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="Y27" s="10" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="Z27" s="10" t="n">
+        <v>3.9</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2802,18 +2844,18 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D28" s="9" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="D28" s="10" t="n">
         <v>29.8</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="10" t="n">
         <v>9.6</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2826,52 +2868,52 @@
         <v>3.8</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L28" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="L28" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="10" t="n">
         <v>19.2</v>
       </c>
-      <c r="N28" s="9" t="n">
+      <c r="N28" s="10" t="n">
         <v>22.2</v>
       </c>
-      <c r="O28" s="9" t="n">
+      <c r="O28" s="10" t="n">
         <v>91.7</v>
       </c>
-      <c r="P28" s="9" t="n">
+      <c r="P28" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="10" t="n">
         <v>28.2</v>
       </c>
-      <c r="R28" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="S28" s="9" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="T28" s="9" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="U28" s="9" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="V28" s="3" t="n">
+      <c r="R28" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="S28" s="10" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="T28" s="10" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="U28" s="10" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V28" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="W28" s="16" t="n">
-        <v>95.61</v>
-      </c>
-      <c r="X28" s="3" t="n">
+      <c r="W28" s="10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="X28" s="10" t="n">
         <v>27.6</v>
       </c>
-      <c r="Y28" s="3" t="n">
+      <c r="Y28" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="Z28" s="3" t="n">
-        <v>16</v>
+      <c r="Z28" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2889,73 +2931,73 @@
       <c r="C29" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="D29" s="9" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F29" s="9" t="n">
+      <c r="D29" s="10" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F29" s="10" t="n">
         <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L29" s="9" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L29" s="10" t="n">
         <v>20.3</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="10" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="9" t="n">
+      <c r="N29" s="10" t="n">
         <v>22.2</v>
       </c>
-      <c r="O29" s="9" t="n">
+      <c r="O29" s="10" t="n">
         <v>93.40000000000001</v>
       </c>
-      <c r="P29" s="9" t="n">
+      <c r="P29" s="10" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="S29" s="9" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="T29" s="9" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="U29" s="9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="V29" s="9" t="n">
+      <c r="R29" s="10" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S29" s="10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="T29" s="10" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="U29" s="10" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="V29" s="10" t="n">
         <v>25.5</v>
       </c>
-      <c r="W29" s="9" t="n">
+      <c r="W29" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="X29" s="9" t="n">
+      <c r="X29" s="10" t="n">
         <v>26.5</v>
       </c>
-      <c r="Y29" s="9" t="n">
+      <c r="Y29" s="10" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="Z29" s="9" t="n">
+      <c r="Z29" s="10" t="n">
         <v>6.1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -2972,22 +3014,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11856.4</v>
-      </c>
-      <c r="D30" s="9" t="n">
-        <v>150.5</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="F30" s="9" t="n">
+        <v>1856.4</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>150.4</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="F30" s="10" t="n">
         <v>124.1</v>
       </c>
-      <c r="G30" s="9" t="n">
-        <v>52.5</v>
+      <c r="G30" s="19" t="n">
+        <v>15.2</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>9.1</v>
+        <v>191.7</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10</v>
@@ -2995,53 +3037,53 @@
       <c r="J30" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K30" s="18" t="n">
+      <c r="K30" s="22" t="n">
         <v>25.4</v>
       </c>
-      <c r="L30" s="9" t="n">
+      <c r="L30" s="10" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="10" t="n">
         <v>93.2</v>
       </c>
-      <c r="N30" s="3" t="n">
-        <v>103.4</v>
-      </c>
-      <c r="O30" s="3" t="n">
-        <v>441.9</v>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Q30" s="9" t="n">
-        <v>138.7</v>
-      </c>
-      <c r="R30" s="9" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>122.7</v>
-      </c>
-      <c r="T30" s="3" t="n">
-        <v>332.8</v>
-      </c>
-      <c r="U30" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="V30" s="18" t="n">
+      <c r="N30" s="10" t="n">
+        <v>813.5</v>
+      </c>
+      <c r="O30" s="10" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="P30" s="10" t="n">
+        <v>219</v>
+      </c>
+      <c r="Q30" s="10" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="R30" s="22" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="S30" s="10" t="n">
+        <v>1693.9</v>
+      </c>
+      <c r="T30" s="10" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="U30" s="10" t="n">
+        <v>2008.7</v>
+      </c>
+      <c r="V30" s="10" t="n">
         <v>123.1</v>
       </c>
-      <c r="W30" s="18" t="n">
+      <c r="W30" s="22" t="n">
         <v>110.1</v>
       </c>
-      <c r="X30" s="3" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="Y30" s="3" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="Z30" s="3" t="n">
-        <v>32.6</v>
+      <c r="X30" s="10" t="n">
+        <v>1498.4</v>
+      </c>
+      <c r="Y30" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z30" s="10" t="n">
+        <v>808.5</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3057,73 +3099,77 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E31" s="9" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E31" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="10" t="n">
         <v>24.8</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" s="10" t="n">
         <v>10.5</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="H31" s="18" t="n">
         <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="N31" s="9" t="n">
+      <c r="N31" s="10" t="n">
         <v>21.4</v>
       </c>
-      <c r="O31" s="9" t="n">
+      <c r="O31" s="10" t="n">
         <v>92.2</v>
       </c>
-      <c r="P31" s="9" t="n">
+      <c r="P31" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="10" t="n">
         <v>27.7</v>
       </c>
-      <c r="R31" s="18" t="n">
+      <c r="R31" s="22" t="n">
         <v>22.7</v>
       </c>
-      <c r="S31" s="9" t="n">
+      <c r="S31" s="10" t="n">
         <v>27.6</v>
       </c>
-      <c r="T31" s="9" t="n">
+      <c r="T31" s="10" t="n">
         <v>74.2</v>
       </c>
-      <c r="U31" s="9" t="n">
+      <c r="U31" s="10" t="n">
         <v>9.6</v>
       </c>
-      <c r="V31" s="18" t="n">
-        <v>824.6</v>
-      </c>
-      <c r="W31" s="18" t="n">
+      <c r="V31" s="10" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="W31" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="X31" s="3" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="Z31" s="3" t="inlineStr"/>
+      <c r="X31" s="10" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="Y31" s="10" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="Z31" s="10" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3138,76 +3184,76 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>143.7</v>
-      </c>
-      <c r="D32" s="9" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="E32" s="9" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="E32" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="F32" s="9" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="G32" s="3" t="n">
+      <c r="F32" s="10" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="G32" s="18" t="n">
         <v>12.6</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="10" t="n">
         <v>19.3</v>
       </c>
-      <c r="N32" s="9" t="n">
+      <c r="N32" s="10" t="n">
         <v>22.4</v>
       </c>
-      <c r="O32" s="9" t="n">
+      <c r="O32" s="10" t="n">
         <v>92.3</v>
       </c>
-      <c r="P32" s="9" t="n">
+      <c r="P32" s="10" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="R32" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="S32" s="3" t="n">
+      <c r="R32" s="10" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="S32" s="10" t="n">
         <v>25.4</v>
       </c>
-      <c r="T32" s="3" t="n">
+      <c r="T32" s="10" t="n">
         <v>56.6</v>
       </c>
-      <c r="U32" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V32" s="3" t="n">
+      <c r="U32" s="10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="V32" s="10" t="n">
         <v>28.2</v>
       </c>
-      <c r="W32" s="13" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X32" s="3" t="n">
+      <c r="W32" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="X32" s="10" t="n">
         <v>26.4</v>
       </c>
-      <c r="Y32" s="3" t="n">
-        <v>169.1</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>111.8</v>
+      <c r="Y32" s="10" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="Z32" s="10" t="n">
+        <v>11.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3223,18 +3269,18 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>310.1</v>
-      </c>
-      <c r="D33" s="9" t="n">
+        <v>397.9</v>
+      </c>
+      <c r="D33" s="10" t="n">
         <v>33.6</v>
       </c>
-      <c r="E33" s="9" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G33" s="9" t="n">
+      <c r="E33" s="10" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G33" s="10" t="n">
         <v>13.9</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3244,55 +3290,55 @@
         <v>4.4</v>
       </c>
       <c r="J33" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="10" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M33" s="10" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N33" s="10" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="O33" s="10" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="P33" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q33" s="10" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="R33" s="10" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="S33" s="10" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="T33" s="10" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="U33" s="10" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="V33" s="10" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="W33" s="10" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X33" s="10" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="Y33" s="10" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="Z33" s="10" t="n">
         <v>5.5</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L33" s="9" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="M33" s="9" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N33" s="9" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="O33" s="9" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="P33" s="9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q33" s="9" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="R33" s="9" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="S33" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="T33" s="9" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="Y33" s="3" t="n">
-        <v>1727.6</v>
-      </c>
-      <c r="Z33" s="3" t="n">
-        <v>7.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3308,76 +3354,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="D34" s="9" t="n">
+        <v>1362.4</v>
+      </c>
+      <c r="D34" s="10" t="n">
         <v>30.4</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="10" t="n">
         <v>25.3</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="10" t="n">
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="L34" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L34" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="N34" s="9" t="n">
+      <c r="N34" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="O34" s="9" t="n">
+      <c r="O34" s="10" t="n">
         <v>91.7</v>
       </c>
-      <c r="P34" s="9" t="n">
+      <c r="P34" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="10" t="n">
         <v>26.1</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" s="10" t="n">
         <v>22.1</v>
       </c>
-      <c r="S34" s="9" t="n">
+      <c r="S34" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="T34" s="9" t="n">
+      <c r="T34" s="10" t="n">
         <v>78.59999999999999</v>
       </c>
-      <c r="U34" s="9" t="n">
+      <c r="U34" s="10" t="n">
         <v>7.2</v>
       </c>
-      <c r="V34" s="13" t="n">
+      <c r="V34" s="10" t="n">
         <v>25.5</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="10" t="n">
         <v>23.3</v>
       </c>
-      <c r="X34" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="Y34" s="3" t="n">
-        <v>182.8</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>5.4</v>
+      <c r="X34" s="10" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y34" s="10" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="Z34" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3395,20 +3441,20 @@
       <c r="C35" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="10" t="n">
         <v>20.8</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="10" t="n">
         <v>3.9</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>1.8</v>
+        <v>18.7</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>0.3</v>
@@ -3419,50 +3465,50 @@
       <c r="K35" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L35" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="M35" s="9" t="n">
+      <c r="L35" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M35" s="10" t="n">
         <v>19.3</v>
       </c>
-      <c r="N35" s="9" t="n">
+      <c r="N35" s="10" t="n">
         <v>22.4</v>
       </c>
-      <c r="O35" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="P35" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q35" s="9" t="n">
+      <c r="O35" s="10" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="P35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="R35" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="S35" s="3" t="n">
+      <c r="R35" s="10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S35" s="10" t="n">
         <v>24.3</v>
       </c>
-      <c r="T35" s="3" t="n">
+      <c r="T35" s="10" t="n">
         <v>88.5</v>
       </c>
-      <c r="U35" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="W35" s="3" t="n">
+      <c r="U35" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V35" s="10" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="W35" s="10" t="n">
         <v>20.3</v>
       </c>
-      <c r="X35" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>2.9</v>
+      <c r="X35" s="10" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="Y35" s="10" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="Z35" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3480,73 +3526,75 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="10" t="n">
         <v>24.3</v>
       </c>
-      <c r="G36" s="9" t="n">
+      <c r="G36" s="10" t="n">
         <v>8.6</v>
       </c>
-      <c r="H36" s="3" t="n">
-        <v>190.1</v>
+      <c r="H36" s="18" t="n">
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="N36" s="9" t="n">
+      <c r="N36" s="10" t="n">
         <v>22.5</v>
       </c>
-      <c r="O36" s="9" t="n">
+      <c r="O36" s="10" t="n">
         <v>92.8</v>
       </c>
-      <c r="P36" s="9" t="n">
+      <c r="P36" s="10" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="S36" s="9" t="n">
+      <c r="S36" s="10" t="n">
         <v>25.8</v>
       </c>
-      <c r="T36" s="9" t="n">
+      <c r="T36" s="10" t="n">
         <v>72.3</v>
       </c>
-      <c r="U36" s="9" t="n">
+      <c r="U36" s="10" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="16" t="n">
-        <v>58</v>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="Y36" s="3" t="n">
+      <c r="V36" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="W36" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="X36" s="10" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="Y36" s="10" t="n">
         <v>78.2</v>
       </c>
-      <c r="Z36" s="3" t="inlineStr"/>
+      <c r="Z36" s="10" t="n">
+        <v>6.9</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3561,19 +3609,19 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>11683.5</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>101</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>127.8</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>49.2</v>
+        <v>168.3</v>
+      </c>
+      <c r="D37" s="22" t="n">
+        <v>150.1</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="F37" s="22" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>14.9</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.40000000000001</v>
@@ -3584,53 +3632,53 @@
       <c r="J37" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="K37" s="18" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L37" s="9" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="M37" s="18" t="n">
+      <c r="K37" s="22" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="L37" s="10" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="M37" s="22" t="n">
         <v>96.5</v>
       </c>
-      <c r="N37" s="9" t="n">
-        <v>921</v>
-      </c>
-      <c r="O37" s="9" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="P37" s="9" t="n">
-        <v>267.8</v>
-      </c>
-      <c r="Q37" s="9" t="n">
+      <c r="N37" s="3" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="Q37" s="10" t="n">
         <v>139.6</v>
       </c>
-      <c r="R37" s="18" t="n">
+      <c r="R37" s="22" t="n">
         <v>115.4</v>
       </c>
-      <c r="S37" s="3" t="n">
-        <v>1256</v>
-      </c>
-      <c r="T37" s="3" t="n">
-        <v>343.7</v>
-      </c>
-      <c r="U37" s="3" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="V37" s="18" t="n">
+      <c r="S37" s="10" t="n">
+        <v>1793.3</v>
+      </c>
+      <c r="T37" s="10" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="U37" s="10" t="n">
+        <v>2031</v>
+      </c>
+      <c r="V37" s="10" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="18" t="n">
+      <c r="W37" s="22" t="n">
         <v>112.2</v>
       </c>
-      <c r="X37" s="3" t="n">
-        <v>127.1</v>
-      </c>
-      <c r="Y37" s="3" t="n">
-        <v>396.6</v>
-      </c>
-      <c r="Z37" s="3" t="n">
-        <v>34.4</v>
+      <c r="X37" s="10" t="n">
+        <v>1610</v>
+      </c>
+      <c r="Y37" s="10" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="Z37" s="10" t="n">
+        <v>927.4</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3646,18 +3694,18 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>336.7</v>
-      </c>
-      <c r="D38" s="18" t="n">
+        <v>2326.7</v>
+      </c>
+      <c r="D38" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="18" t="n">
+      <c r="F38" s="22" t="n">
         <v>25.1</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3667,55 +3715,55 @@
         <v>2.5</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L38" s="9" t="n">
+      <c r="L38" s="10" t="n">
         <v>20.7</v>
       </c>
-      <c r="M38" s="9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N38" s="9" t="n">
+      <c r="M38" s="10" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="10" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="R38" s="22" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="S38" s="10" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="T38" s="10" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="U38" s="10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="V38" s="10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="W38" s="22" t="n">
         <v>22.4</v>
       </c>
-      <c r="O38" s="9" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="P38" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q38" s="9" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="R38" s="18" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="T38" s="3" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="V38" s="18" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="W38" s="18" t="n">
-        <v>224.1</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="Y38" s="3" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v>16.9</v>
+      <c r="X38" s="10" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="Y38" s="10" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="Z38" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3731,74 +3779,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>400.8</v>
-      </c>
-      <c r="D39" s="9" t="n">
+        <v>1400.8</v>
+      </c>
+      <c r="D39" s="10" t="n">
         <v>31.9</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="10" t="n">
         <v>25.6</v>
       </c>
-      <c r="G39" s="13" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="H39" s="13" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="I39" s="3" t="inlineStr"/>
+      <c r="G39" s="10" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>2.5</v>
+      </c>
       <c r="J39" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="10" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="13" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Q39" s="16" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="R39" s="9" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="T39" s="3" t="n">
+      <c r="N39" s="10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="O39" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="P39" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q39" s="10" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="R39" s="10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="S39" s="10" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="T39" s="10" t="n">
         <v>54.5</v>
       </c>
-      <c r="U39" s="3" t="n">
+      <c r="U39" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="W39" s="3" t="n">
+      <c r="W39" s="10" t="n">
         <v>23.8</v>
       </c>
-      <c r="X39" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="Z39" s="3" t="n">
-        <v>3.6</v>
+      <c r="X39" s="10" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="Y39" s="10" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="Z39" s="10" t="n">
+        <v>5.8</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3816,20 +3866,20 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="9" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F40" s="9" t="n">
+      <c r="D40" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F40" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H40" s="13" t="n">
-        <v>89</v>
+        <v>13.9</v>
+      </c>
+      <c r="H40" s="18" t="n">
+        <v>129</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.4</v>
@@ -3840,50 +3890,50 @@
       <c r="K40" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="10" t="n">
         <v>19.1</v>
       </c>
-      <c r="N40" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q40" s="9" t="n">
+      <c r="N40" s="10" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="O40" s="10" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="P40" s="10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q40" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" s="10" t="n">
         <v>19.2</v>
       </c>
-      <c r="S40" s="9" t="n">
+      <c r="S40" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="T40" s="9" t="n">
+      <c r="T40" s="10" t="n">
         <v>89.7</v>
       </c>
-      <c r="U40" s="9" t="n">
+      <c r="U40" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="13" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y40" s="3" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="Z40" s="3" t="n">
-        <v>15.9</v>
+      <c r="V40" s="10" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="W40" s="10" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="X40" s="10" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="Y40" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z40" s="10" t="n">
+        <v>2.5</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3899,15 +3949,15 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E41" s="9" t="n">
+        <v>244.8</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E41" s="10" t="n">
         <v>19.5</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="10" t="n">
         <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3917,7 +3967,7 @@
         <v>17.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>3.8</v>
@@ -3925,50 +3975,50 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="10" t="n">
         <v>18.7</v>
       </c>
-      <c r="N41" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q41" s="3" t="n">
+      <c r="N41" s="10" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="O41" s="10" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="P41" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q41" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="V41" s="3" t="n">
+      <c r="S41" s="10" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="T41" s="10" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="U41" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="V41" s="10" t="n">
         <v>24.6</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W41" s="10" t="n">
         <v>22.2</v>
       </c>
-      <c r="X41" s="13" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>19.6</v>
+      <c r="X41" s="10" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="Y41" s="10" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="Z41" s="10" t="n">
+        <v>4.2</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3984,18 +4034,18 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1464.5</v>
-      </c>
-      <c r="D42" s="9" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="D42" s="10" t="n">
         <v>32.8</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="10" t="n">
         <v>24.9</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="18" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4010,50 +4060,50 @@
       <c r="K42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L42" s="9" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="M42" s="3" t="n">
+      <c r="L42" s="10" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="M42" s="10" t="n">
         <v>16.1</v>
       </c>
-      <c r="N42" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Q42" s="3" t="n">
+      <c r="N42" s="10" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="O42" s="10" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="P42" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q42" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="S42" s="13" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="V42" s="3" t="n">
+      <c r="S42" s="10" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="T42" s="10" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="U42" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="V42" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="W42" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v>182</v>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v>8.699999999999999</v>
+      <c r="W42" s="10" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X42" s="10" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="Y42" s="10" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="Z42" s="10" t="n">
+        <v>7.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4069,18 +4119,18 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="D43" s="9" t="n">
+        <v>2341.3</v>
+      </c>
+      <c r="D43" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="10" t="n">
         <v>25.3</v>
       </c>
-      <c r="G43" s="9" t="n">
+      <c r="G43" s="10" t="n">
         <v>13.4</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4095,50 +4145,50 @@
       <c r="K43" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="L43" s="9" t="n">
+      <c r="L43" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="10" t="n">
         <v>17.7</v>
       </c>
-      <c r="N43" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q43" s="3" t="n">
+      <c r="N43" s="10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="O43" s="10" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="P43" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q43" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="9" t="n">
+      <c r="R43" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="S43" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V43" s="3" t="n">
+      <c r="S43" s="10" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="T43" s="10" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="U43" s="10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V43" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="W43" s="3" t="n">
+      <c r="W43" s="10" t="n">
         <v>22.4</v>
       </c>
-      <c r="X43" s="3" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="Y43" s="3" t="n">
-        <v>182.8</v>
-      </c>
-      <c r="Z43" s="3" t="n">
-        <v>14.6</v>
+      <c r="X43" s="10" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="Y43" s="10" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4156,16 +4206,16 @@
       <c r="C44" s="3" t="n">
         <v>141.6</v>
       </c>
-      <c r="D44" s="9" t="n">
+      <c r="D44" s="10" t="n">
         <v>23.9</v>
       </c>
-      <c r="E44" s="9" t="n">
+      <c r="E44" s="10" t="n">
         <v>19.1</v>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="F44" s="10" t="n">
         <v>21.4</v>
       </c>
-      <c r="G44" s="9" t="n">
+      <c r="G44" s="10" t="n">
         <v>4.9</v>
       </c>
       <c r="H44" s="3" t="n">
@@ -4175,48 +4225,56 @@
         <v>0.8</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="L44" s="9" t="n">
+      <c r="L44" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>890.1</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q44" s="3" t="n">
+      <c r="M44" s="10" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N44" s="10" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="O44" s="10" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="P44" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q44" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="R44" s="9" t="n">
+      <c r="R44" s="10" t="n">
         <v>20.3</v>
       </c>
-      <c r="S44" s="3" t="n">
+      <c r="S44" s="10" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="T44" s="10" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="U44" s="10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V44" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="T44" s="3" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="W44" s="12" t="inlineStr"/>
-      <c r="X44" s="3" t="inlineStr"/>
-      <c r="Y44" s="3" t="inlineStr"/>
-      <c r="Z44" s="3" t="inlineStr"/>
+      <c r="W44" s="10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X44" s="10" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="Y44" s="10" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="Z44" s="10" t="n">
+        <v>3.3</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4231,74 +4289,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>168211.1</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>174.6</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>113.4</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>143.8</v>
+        <v>1.8</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>174</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>114</v>
+      </c>
+      <c r="F45" s="22" t="n">
+        <v>144</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>10.6</v>
+        <v>60.2</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>2637</v>
+        <v>105.6</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>183.3</v>
+        <v>13.3</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="K45" s="18" t="n">
-        <v>28</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="M45" s="14" t="inlineStr"/>
+      <c r="K45" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="L45" s="10" t="n">
+        <v>117</v>
+      </c>
+      <c r="M45" s="10" t="n">
+        <v>109.2</v>
+      </c>
       <c r="N45" s="3" t="n">
-        <v>10092105.9</v>
+        <v>1218.1</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>34.2</v>
+        <v>534.4</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>140.4</v>
       </c>
-      <c r="Q45" s="18" t="n">
-        <v>257.5</v>
-      </c>
-      <c r="R45" s="9" t="n">
-        <v>129.1</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>1382</v>
-      </c>
-      <c r="T45" s="3" t="n">
-        <v>484</v>
-      </c>
-      <c r="U45" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V45" s="18" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="W45" s="18" t="n">
-        <v>182.2</v>
+      <c r="Q45" s="10" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="R45" s="22" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="S45" s="10" t="n">
+        <v>2839</v>
+      </c>
+      <c r="T45" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="U45" s="10" t="n">
+        <v>3474.7</v>
+      </c>
+      <c r="V45" s="10" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="W45" s="10" t="n">
+        <v>132</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>24.7</v>
+        <v>2485.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>81.5</v>
+        <v>48390.4</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>5.8</v>
+        <v>124.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4316,20 +4376,20 @@
       <c r="C46" s="3" t="n">
         <v>311.7</v>
       </c>
-      <c r="D46" s="9" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F46" s="9" t="n">
+      <c r="D46" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="F46" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="9" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H46" s="13" t="n">
-        <v>17.6</v>
+      <c r="G46" s="18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H46" s="18" t="n">
+        <v>167.6</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>2.2</v>
@@ -4337,50 +4397,52 @@
       <c r="J46" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L46" s="9" t="n">
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="10" t="n">
         <v>18.2</v>
       </c>
-      <c r="N46" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q46" s="18" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="R46" s="9" t="n">
+      <c r="N46" s="10" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="O46" s="10" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="P46" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q46" s="10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R46" s="22" t="n">
         <v>21.6</v>
       </c>
-      <c r="S46" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V46" s="18" t="n">
+      <c r="S46" s="10" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="T46" s="10" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="U46" s="10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V46" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="18" t="n">
+      <c r="W46" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="X46" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="Y46" s="3" t="inlineStr"/>
-      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="X46" s="10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="Y46" s="10" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="Z46" s="10" t="n">
+        <v>4.1</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
